--- a/results/block2_results/stenosis/Normal_1/branches/dataframes/dataset_LCA_B06_Normal_1.xlsx
+++ b/results/block2_results/stenosis/Normal_1/branches/dataframes/dataset_LCA_B06_Normal_1.xlsx
@@ -553,14 +553,14 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>12.94918332241907</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="b">
@@ -606,14 +606,14 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L3" t="n">
         <v>0.1412437639641267</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>12.94918332241907</v>
+        <v>25.67335572679642</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="b">
@@ -659,14 +659,14 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L4" t="n">
         <v>0.1418041999892184</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>12.94918332241907</v>
+        <v>25.67335572679642</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="b">
@@ -712,14 +712,14 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L5" t="n">
         <v>0.1462774201209379</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>12.94918332241907</v>
+        <v>25.67335572679642</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="b">
@@ -765,14 +765,14 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="L6" t="n">
         <v>0.5960228711038292</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>13.74461230569916</v>
+        <v>22.40658457261621</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="b">
@@ -818,14 +818,14 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
       <c r="L7" t="n">
         <v>0.7307865025728671</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>14.01711486461985</v>
+        <v>22.66819578486057</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="b">
@@ -871,14 +871,14 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
       <c r="L8" t="n">
         <v>0.9035407319073603</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>14.01711486461985</v>
+        <v>22.66819578486057</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="b">
@@ -924,14 +924,14 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L9" t="n">
         <v>1.068746663715582</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>14.25821179004597</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="b">
@@ -977,14 +977,14 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L10" t="n">
         <v>1.087154158780691</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>14.25821179004597</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="b">
@@ -1030,14 +1030,14 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L11" t="n">
         <v>1.087375279641611</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>14.25821179004597</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="b">
@@ -1083,14 +1083,14 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
       <c r="L12" t="n">
         <v>1.337704961978807</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>14.35948117378207</v>
+        <v>31.27985483414414</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="b">
@@ -1136,14 +1136,14 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="L13" t="n">
         <v>1.338703830096165</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>14.35948117378207</v>
+        <v>31.27985483414414</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="b">
@@ -1189,14 +1189,14 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="L14" t="n">
         <v>1.650851799473779</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>14.39337587577508</v>
+        <v>28.56331160274965</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="b">
@@ -1242,14 +1242,14 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="L15" t="n">
         <v>2.018967951978974</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>14.33776555810451</v>
+        <v>10.16809568606692</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="b">
@@ -1295,14 +1295,14 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
       <c r="L16" t="n">
         <v>2.240089092139182</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>14.33776555810451</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="b">
@@ -1348,14 +1348,14 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
       <c r="L17" t="n">
         <v>2.28202895297122</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>14.46751017667901</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="b">
@@ -1401,14 +1401,14 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
       <c r="L18" t="n">
         <v>2.709109177917012</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>14.90065600322594</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="b">
@@ -1454,14 +1454,14 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L19" t="n">
         <v>3.000430953050925</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>15.10789666146953</v>
+        <v>9.305111203703676</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="b">
@@ -1507,14 +1507,14 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L20" t="n">
         <v>3.044336945982316</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>15.10789666146953</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="b">
@@ -1560,14 +1560,14 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L21" t="n">
         <v>3.044508225464774</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>15.10789666146953</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="b">
@@ -1613,14 +1613,14 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
       <c r="L22" t="n">
         <v>3.36547051777895</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>15.28683754312319</v>
+        <v>9.671360125421126</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="b">
@@ -1666,14 +1666,14 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
       <c r="L23" t="n">
         <v>3.609930529204121</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>15.45586864838683</v>
+        <v>9.713089998084643</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="b">
@@ -1719,14 +1719,14 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
       <c r="L24" t="n">
         <v>3.826624684422638</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>15.45586864838683</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="b">
@@ -1772,14 +1772,14 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
       <c r="L25" t="n">
         <v>3.99764735007134</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>38.49477201445094</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="b">
@@ -1825,14 +1825,14 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
       <c r="L26" t="n">
         <v>4.062919325765148</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>38.49477201445094</v>
+        <v>10.04075472918658</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="b">
@@ -1878,14 +1878,14 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
       <c r="L27" t="n">
         <v>4.063188092778018</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>38.49477201445094</v>
+        <v>10.04075472918658</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="b">
@@ -1931,14 +1931,14 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
       <c r="L28" t="n">
         <v>4.343621288744651</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>50.66302055048502</v>
+        <v>10.14534989254991</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="b">
@@ -1984,14 +1984,14 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
       <c r="L29" t="n">
         <v>4.701833908505561</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>73.02287512573871</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="b">
@@ -2037,14 +2037,14 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
       <c r="L30" t="n">
         <v>4.860241057422114</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>27.5466963351074</v>
+        <v>10.60555613158018</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="b">
@@ -2090,26 +2090,20 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
       <c r="L31" t="n">
         <v>5.043919493699776</v>
       </c>
-      <c r="M31" t="n">
-        <v>24.44938674448072</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>25.49347212687086</v>
-      </c>
-      <c r="O31" t="n">
-        <v>24.97142943567579</v>
-      </c>
+        <v>10.62865290898554</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>48.14400450813188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2149,26 +2143,20 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
       <c r="L32" t="n">
         <v>5.362812728454265</v>
       </c>
-      <c r="M32" t="n">
-        <v>23.09469567725773</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>21.33836097537404</v>
-      </c>
-      <c r="O32" t="n">
-        <v>22.21652832631588</v>
-      </c>
+        <v>10.88520124779484</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>40.17055030728073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2208,26 +2196,20 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="L33" t="n">
         <v>5.365503515425706</v>
       </c>
-      <c r="M33" t="n">
-        <v>23.09469567725773</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>21.33836097537404</v>
-      </c>
-      <c r="O33" t="n">
-        <v>22.21652832631588</v>
-      </c>
+        <v>10.88520124779484</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>40.17055030728073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2267,26 +2249,20 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
       <c r="L34" t="n">
         <v>5.637989398143552</v>
       </c>
-      <c r="M34" t="n">
-        <v>16.22537890841612</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>21.36069899557773</v>
-      </c>
-      <c r="O34" t="n">
-        <v>18.79303895199693</v>
-      </c>
+        <v>10.96189869435236</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>26.86327985161404</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2326,26 +2302,20 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="L35" t="n">
         <v>5.818522700014498</v>
       </c>
-      <c r="M35" t="n">
-        <v>15.55123726155539</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>23.60395345894496</v>
-      </c>
-      <c r="O35" t="n">
-        <v>19.57759536025018</v>
-      </c>
+        <v>11.01112865213726</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>28.40226490184888</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2385,26 +2355,20 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.25821179004597</v>
+        <v>14.26268479452115</v>
       </c>
       <c r="L36" t="n">
         <v>6.031714496035897</v>
       </c>
-      <c r="M36" t="n">
-        <v>15.50392193361757</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>30.32524846705273</v>
-      </c>
-      <c r="O36" t="n">
-        <v>22.91458520033515</v>
-      </c>
+        <v>11.018354095561</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>37.77669695789464</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2444,26 +2408,20 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.35948117378207</v>
+        <v>14.35993720530086</v>
       </c>
       <c r="L37" t="n">
         <v>6.293349752075791</v>
       </c>
-      <c r="M37" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>33.1118269799849</v>
-      </c>
-      <c r="O37" t="n">
-        <v>24.01283173498727</v>
-      </c>
+        <v>10.89968555114491</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>40.20080042096841</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2503,26 +2461,20 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.35948117378207</v>
+        <v>14.35993720530086</v>
       </c>
       <c r="L38" t="n">
         <v>6.303460251500643</v>
       </c>
-      <c r="M38" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>93.42524075950476</v>
-      </c>
-      <c r="O38" t="n">
-        <v>54.1695386247472</v>
-      </c>
+        <v>10.89968555114491</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>73.49159409819676</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2562,26 +2514,20 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.39337587577508</v>
+        <v>14.39231959267601</v>
       </c>
       <c r="L39" t="n">
         <v>6.658290468760159</v>
       </c>
-      <c r="M39" t="n">
-        <v>13.96252814601202</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>29.05532579013986</v>
-      </c>
-      <c r="O39" t="n">
-        <v>21.50892696807594</v>
-      </c>
+        <v>10.53428444199073</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>33.08185063281831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2621,26 +2567,20 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.33776555810451</v>
+        <v>14.34250198872172</v>
       </c>
       <c r="L40" t="n">
         <v>7.017532808796264</v>
       </c>
-      <c r="M40" t="n">
-        <v>12.8845474029381</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>10.21282575007027</v>
-      </c>
-      <c r="O40" t="n">
-        <v>11.54868657650418</v>
-      </c>
+        <v>9.547526235149299</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>-24.1506162897754</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2680,26 +2620,20 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.33776555810451</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="L41" t="n">
         <v>7.021890976463653</v>
       </c>
-      <c r="M41" t="n">
-        <v>12.8845474029381</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>10.21282575007027</v>
-      </c>
-      <c r="O41" t="n">
-        <v>11.54868657650418</v>
-      </c>
+        <v>9.547526235149299</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>-24.1506162897754</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2739,26 +2673,20 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.33776555810451</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="L42" t="n">
         <v>7.045348263062365</v>
       </c>
-      <c r="M42" t="n">
-        <v>12.8845474029381</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>9.761777786710743</v>
-      </c>
-      <c r="O42" t="n">
-        <v>11.32316259482442</v>
-      </c>
+        <v>9.547526235149299</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>-26.62333016977074</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2798,26 +2726,20 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.46751017667901</v>
+        <v>14.46958771214976</v>
       </c>
       <c r="L43" t="n">
         <v>7.482586175113796</v>
       </c>
-      <c r="M43" t="n">
-        <v>12.56557511094277</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>9.33637179119815</v>
-      </c>
-      <c r="O43" t="n">
-        <v>10.95097345107046</v>
-      </c>
+        <v>8.766071098486607</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>-32.11163593191628</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2857,26 +2779,20 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.90065600322594</v>
+        <v>14.88833480134777</v>
       </c>
       <c r="L44" t="n">
         <v>7.827223320062904</v>
       </c>
-      <c r="M44" t="n">
-        <v>12.42650727241244</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>9.290631264491166</v>
-      </c>
-      <c r="O44" t="n">
-        <v>10.8585692684518</v>
-      </c>
+        <v>8.660472291933454</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>-37.22485564021687</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2916,26 +2832,20 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>15.10789666146953</v>
+        <v>15.08131980831518</v>
       </c>
       <c r="L45" t="n">
         <v>8.029624203985836</v>
       </c>
-      <c r="M45" t="n">
-        <v>12.6149723565889</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>9.452446335487469</v>
-      </c>
-      <c r="O45" t="n">
-        <v>11.03370934603819</v>
-      </c>
+        <v>8.87437875450698</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-36.92491063210974</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2975,26 +2885,20 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>15.24076100085329</v>
+        <v>15.23824314337372</v>
       </c>
       <c r="L46" t="n">
         <v>8.289235253359951</v>
       </c>
-      <c r="M46" t="n">
-        <v>12.88726856229838</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>9.661749357520293</v>
-      </c>
-      <c r="O46" t="n">
-        <v>11.27450895990934</v>
-      </c>
+        <v>8.973642303512785</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-35.17893377926635</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3034,26 +2938,20 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>15.28683754312319</v>
+        <v>15.31237881114555</v>
       </c>
       <c r="L47" t="n">
         <v>8.406390589508277</v>
       </c>
-      <c r="M47" t="n">
-        <v>12.88726856229838</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>9.661749357520293</v>
-      </c>
-      <c r="O47" t="n">
-        <v>11.27450895990934</v>
-      </c>
+        <v>8.973642303512785</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>-35.58761270651489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3093,26 +2991,20 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>15.28683754312319</v>
+        <v>15.31237881114555</v>
       </c>
       <c r="L48" t="n">
         <v>8.407327639434872</v>
       </c>
-      <c r="M48" t="n">
-        <v>12.88726856229838</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>9.661749357520293</v>
-      </c>
-      <c r="O48" t="n">
-        <v>11.27450895990934</v>
-      </c>
+        <v>8.973642303512785</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-35.58761270651489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3152,26 +3044,20 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.45586864838683</v>
+        <v>15.53738489344973</v>
       </c>
       <c r="L49" t="n">
         <v>8.621179285071337</v>
       </c>
-      <c r="M49" t="n">
-        <v>13.08268414389388</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>9.737462158199968</v>
-      </c>
-      <c r="O49" t="n">
-        <v>11.41007315104692</v>
-      </c>
+        <v>9.158898762760314</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>-35.45810306193078</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3211,26 +3097,20 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>38.49477201445094</v>
+        <v>41.85527415873189</v>
       </c>
       <c r="L50" t="n">
         <v>9.210682480011656</v>
       </c>
-      <c r="M50" t="n">
-        <v>12.82946633796654</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>10.03578416659066</v>
-      </c>
-      <c r="O50" t="n">
-        <v>11.4326252522786</v>
-      </c>
+        <v>9.403399618816287</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>-236.7098209291752</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3270,26 +3150,20 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>50.66302055048502</v>
+        <v>51.03791363001811</v>
       </c>
       <c r="L51" t="n">
         <v>9.262006823344112</v>
       </c>
-      <c r="M51" t="n">
-        <v>12.82946633796654</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>10.03578416659066</v>
-      </c>
-      <c r="O51" t="n">
-        <v>11.4326252522786</v>
-      </c>
+        <v>9.403399618816287</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>-343.1442423111658</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3329,26 +3203,20 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>50.66302055048502</v>
+        <v>51.03791363001811</v>
       </c>
       <c r="L52" t="n">
         <v>9.263266782683187</v>
       </c>
-      <c r="M52" t="n">
-        <v>12.82946633796654</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>10.03578416659066</v>
-      </c>
-      <c r="O52" t="n">
-        <v>11.4326252522786</v>
-      </c>
+        <v>9.403399618816287</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>-343.1442423111658</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3388,26 +3256,20 @@
         <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>73.02287512573871</v>
+        <v>70.22101375492795</v>
       </c>
       <c r="L53" t="n">
         <v>9.471836756352449</v>
       </c>
-      <c r="M53" t="n">
-        <v>12.82946633796654</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>10.12549314622187</v>
-      </c>
-      <c r="O53" t="n">
-        <v>11.47747974209421</v>
-      </c>
+        <v>9.399987799230123</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>-536.2274363937564</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3447,26 +3309,20 @@
         <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>27.5466963351074</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="L54" t="n">
         <v>9.987006130633025</v>
       </c>
-      <c r="M54" t="n">
-        <v>12.94918332241907</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>10.62248024777271</v>
-      </c>
-      <c r="O54" t="n">
-        <v>11.78583178509589</v>
-      </c>
+        <v>8.778672810676495</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>-133.727214484279</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3506,25 +3362,25 @@
         <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>25.49347212687086</v>
+        <v>25.80032314541072</v>
       </c>
       <c r="L55" t="n">
         <v>10.08607504425238</v>
       </c>
       <c r="M55" t="n">
-        <v>12.94918332241907</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N55" t="n">
-        <v>10.62248024777271</v>
+        <v>8.670969426295731</v>
       </c>
       <c r="O55" t="n">
-        <v>11.78583178509589</v>
+        <v>15.12826573840246</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>-116.3060918543684</v>
+        <v>-70.54382565423671</v>
       </c>
     </row>
     <row r="56">
@@ -3565,25 +3421,25 @@
         <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>23.97322394592734</v>
+        <v>25.67335572679642</v>
       </c>
       <c r="L56" t="n">
         <v>10.14575262718859</v>
       </c>
       <c r="M56" t="n">
-        <v>12.94918332241907</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N56" t="n">
-        <v>10.62248024777271</v>
+        <v>8.670969426295731</v>
       </c>
       <c r="O56" t="n">
-        <v>11.78583178509589</v>
+        <v>15.12826573840246</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>-103.4071449776109</v>
+        <v>-69.70455285978817</v>
       </c>
     </row>
     <row r="57">
@@ -3624,25 +3480,25 @@
         <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>21.33836097537404</v>
+        <v>22.39575428021364</v>
       </c>
       <c r="L57" t="n">
         <v>10.56959374030862</v>
       </c>
       <c r="M57" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N57" t="n">
-        <v>10.92162235687036</v>
+        <v>8.618593561821877</v>
       </c>
       <c r="O57" t="n">
-        <v>12.33311733128476</v>
+        <v>12.45591703567201</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>-73.01676779840696</v>
+        <v>-79.80012403804007</v>
       </c>
     </row>
     <row r="58">
@@ -3683,25 +3539,25 @@
         <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>21.36069899557773</v>
+        <v>22.40658457261621</v>
       </c>
       <c r="L58" t="n">
         <v>10.60890551992495</v>
       </c>
       <c r="M58" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N58" t="n">
-        <v>10.95616069257222</v>
+        <v>8.670332350741491</v>
       </c>
       <c r="O58" t="n">
-        <v>12.35038649913569</v>
+        <v>12.48178643013182</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>-72.95571273880871</v>
+        <v>-79.51424419925426</v>
       </c>
     </row>
     <row r="59">
@@ -3742,25 +3598,25 @@
         <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>21.36069899557773</v>
+        <v>22.40658457261621</v>
       </c>
       <c r="L59" t="n">
         <v>10.60906482635963</v>
       </c>
       <c r="M59" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N59" t="n">
-        <v>10.95616069257222</v>
+        <v>8.670332350741491</v>
       </c>
       <c r="O59" t="n">
-        <v>12.35038649913569</v>
+        <v>12.48178643013182</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>-72.95571273880871</v>
+        <v>-79.51424419925426</v>
       </c>
     </row>
     <row r="60">
@@ -3801,25 +3657,25 @@
         <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>23.60395345894496</v>
+        <v>22.66819578486057</v>
       </c>
       <c r="L60" t="n">
         <v>10.75828331450469</v>
       </c>
       <c r="M60" t="n">
-        <v>14.01711486461985</v>
+        <v>15.99543613326018</v>
       </c>
       <c r="N60" t="n">
-        <v>11.00900355804066</v>
+        <v>8.737214268524154</v>
       </c>
       <c r="O60" t="n">
-        <v>12.51305921133025</v>
+        <v>12.36632520089217</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>-88.63455419097022</v>
+        <v>-83.30583594247689</v>
       </c>
     </row>
     <row r="61">
@@ -3860,25 +3716,25 @@
         <v>6</v>
       </c>
       <c r="K61" t="n">
-        <v>23.60395345894496</v>
+        <v>22.66819578486057</v>
       </c>
       <c r="L61" t="n">
         <v>10.75949080930725</v>
       </c>
       <c r="M61" t="n">
-        <v>14.01711486461985</v>
+        <v>15.99543613326018</v>
       </c>
       <c r="N61" t="n">
-        <v>11.00900355804066</v>
+        <v>8.737214268524154</v>
       </c>
       <c r="O61" t="n">
-        <v>12.51305921133025</v>
+        <v>12.36632520089217</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>-88.63455419097022</v>
+        <v>-83.30583594247689</v>
       </c>
     </row>
     <row r="62">
@@ -3919,25 +3775,25 @@
         <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>30.32524846705273</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="L62" t="n">
         <v>11.14715062133697</v>
       </c>
       <c r="M62" t="n">
-        <v>14.25821179004597</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="N62" t="n">
-        <v>11.01276194340502</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="O62" t="n">
-        <v>12.6354868667255</v>
+        <v>12.3011024820373</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>-140.0006330338703</v>
+        <v>-121.5014269419499</v>
       </c>
     </row>
     <row r="63">
@@ -3978,25 +3834,25 @@
         <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>33.1118269799849</v>
+        <v>29.32917623785547</v>
       </c>
       <c r="L63" t="n">
         <v>11.25146500145535</v>
       </c>
       <c r="M63" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86969785602394</v>
       </c>
       <c r="N63" t="n">
-        <v>10.91014021015967</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="O63" t="n">
-        <v>12.63481069197087</v>
+        <v>11.9759775418505</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>-162.0682476946544</v>
+        <v>-144.9000604365162</v>
       </c>
     </row>
     <row r="64">
@@ -4037,25 +3893,25 @@
         <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>33.1118269799849</v>
+        <v>29.32917623785547</v>
       </c>
       <c r="L64" t="n">
         <v>11.25188434063026</v>
       </c>
       <c r="M64" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86969785602394</v>
       </c>
       <c r="N64" t="n">
-        <v>10.91014021015967</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="O64" t="n">
-        <v>12.63481069197087</v>
+        <v>11.9759775418505</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>-162.0682476946544</v>
+        <v>-144.9000604365162</v>
       </c>
     </row>
     <row r="65">
@@ -4096,25 +3952,25 @@
         <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>93.42524075950476</v>
+        <v>31.27985483414414</v>
       </c>
       <c r="L65" t="n">
         <v>11.34946317165594</v>
       </c>
       <c r="M65" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="N65" t="n">
-        <v>10.91014021015967</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="O65" t="n">
-        <v>12.63481069197087</v>
+        <v>11.97592568894864</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>-639.4273094956168</v>
+        <v>-161.189453296367</v>
       </c>
     </row>
     <row r="66">
@@ -4155,25 +4011,25 @@
         <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>93.42524075950476</v>
+        <v>31.27985483414414</v>
       </c>
       <c r="L66" t="n">
         <v>11.35105010405817</v>
       </c>
       <c r="M66" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="N66" t="n">
-        <v>10.91014021015967</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="O66" t="n">
-        <v>12.63481069197087</v>
+        <v>11.97592568894864</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>-639.4273094956168</v>
+        <v>-161.189453296367</v>
       </c>
     </row>
     <row r="67">
@@ -4214,25 +4070,25 @@
         <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>93.43501340024444</v>
+        <v>31.88841857057561</v>
       </c>
       <c r="L67" t="n">
         <v>11.45548970507953</v>
       </c>
       <c r="M67" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="N67" t="n">
-        <v>10.75714398709465</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="O67" t="n">
-        <v>12.55831258043836</v>
+        <v>12.18140081194954</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>-644.0092990342097</v>
+        <v>-161.7795692207596</v>
       </c>
     </row>
     <row r="68">
@@ -4273,25 +4129,25 @@
         <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>93.43501340024444</v>
+        <v>31.88841857057561</v>
       </c>
       <c r="L68" t="n">
         <v>11.45590597927597</v>
       </c>
       <c r="M68" t="n">
-        <v>14.35948117378207</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="N68" t="n">
-        <v>10.75714398709465</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="O68" t="n">
-        <v>12.55831258043836</v>
+        <v>12.18140081194954</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>-644.0092990342097</v>
+        <v>-161.7795692207596</v>
       </c>
     </row>
     <row r="69">
@@ -4332,25 +4188,25 @@
         <v>6</v>
       </c>
       <c r="K69" t="n">
-        <v>29.05532579013986</v>
+        <v>28.70137421356502</v>
       </c>
       <c r="L69" t="n">
         <v>11.62640760444893</v>
       </c>
       <c r="M69" t="n">
-        <v>14.39337587577508</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N69" t="n">
-        <v>10.53712094521892</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="O69" t="n">
-        <v>12.465248410497</v>
+        <v>11.70592851117332</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>-133.0906279065593</v>
+        <v>-145.1866520982898</v>
       </c>
     </row>
     <row r="70">
@@ -4391,25 +4247,25 @@
         <v>6</v>
       </c>
       <c r="K70" t="n">
-        <v>29.05532579013986</v>
+        <v>28.56331160274965</v>
       </c>
       <c r="L70" t="n">
         <v>11.63576439045102</v>
       </c>
       <c r="M70" t="n">
-        <v>14.39337587577508</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N70" t="n">
-        <v>10.53712094521892</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="O70" t="n">
-        <v>12.465248410497</v>
+        <v>11.70592851117332</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>-133.0906279065593</v>
+        <v>-144.0072274103327</v>
       </c>
     </row>
     <row r="71">
@@ -4450,25 +4306,25 @@
         <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>10.60692062922534</v>
+        <v>10.56353720219123</v>
       </c>
       <c r="L71" t="n">
         <v>11.82340354437543</v>
       </c>
       <c r="M71" t="n">
-        <v>14.39337587577508</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N71" t="n">
-        <v>10.11688682207371</v>
+        <v>9.562461236943456</v>
       </c>
       <c r="O71" t="n">
-        <v>12.25513134892439</v>
+        <v>11.74055539280562</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>13.44914773062562</v>
+        <v>10.02523433717322</v>
       </c>
     </row>
     <row r="72">
@@ -4509,25 +4365,25 @@
         <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>10.24700477381645</v>
+        <v>10.19530365223804</v>
       </c>
       <c r="L72" t="n">
         <v>11.90245691692625</v>
       </c>
       <c r="M72" t="n">
-        <v>14.33776555810451</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="N72" t="n">
-        <v>10.11688682207371</v>
+        <v>9.977092619200015</v>
       </c>
       <c r="O72" t="n">
-        <v>12.22732619008911</v>
+        <v>11.42586365549004</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>16.19586641826738</v>
+        <v>10.76995175468178</v>
       </c>
     </row>
     <row r="73">
@@ -4568,25 +4424,25 @@
         <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>10.21282575007027</v>
+        <v>10.16809568606692</v>
       </c>
       <c r="L73" t="n">
         <v>11.9317524766208</v>
       </c>
       <c r="M73" t="n">
-        <v>14.33776555810451</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="N73" t="n">
-        <v>10.11688682207371</v>
+        <v>9.977092619200015</v>
       </c>
       <c r="O73" t="n">
-        <v>12.22732619008911</v>
+        <v>11.42586365549004</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>16.47539624526986</v>
+        <v>11.0080778779359</v>
       </c>
     </row>
     <row r="74">
@@ -4627,25 +4483,25 @@
         <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>9.761777786710743</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="L74" t="n">
         <v>12.13780394487992</v>
       </c>
       <c r="M74" t="n">
-        <v>14.33776555810451</v>
+        <v>12.56213898660848</v>
       </c>
       <c r="N74" t="n">
-        <v>9.337125357350384</v>
+        <v>10.08724170276781</v>
       </c>
       <c r="O74" t="n">
-        <v>11.83744545772744</v>
+        <v>11.32469034468814</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>17.53476016788498</v>
+        <v>13.97161877321401</v>
       </c>
     </row>
     <row r="75">
@@ -4686,25 +4542,25 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>9.761777786710743</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="L75" t="n">
         <v>12.13862894317027</v>
       </c>
       <c r="M75" t="n">
-        <v>14.33776555810451</v>
+        <v>12.56213898660848</v>
       </c>
       <c r="N75" t="n">
-        <v>9.337125357350384</v>
+        <v>10.08724170276781</v>
       </c>
       <c r="O75" t="n">
-        <v>11.83744545772744</v>
+        <v>11.32469034468814</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>17.53476016788498</v>
+        <v>13.97161877321401</v>
       </c>
     </row>
     <row r="76">
@@ -4745,25 +4601,25 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>9.33637179119815</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="L76" t="n">
         <v>12.65145568829585</v>
       </c>
       <c r="M76" t="n">
-        <v>14.46751017667901</v>
+        <v>12.41804037237105</v>
       </c>
       <c r="N76" t="n">
-        <v>8.704344846279827</v>
+        <v>10.26722045282886</v>
       </c>
       <c r="O76" t="n">
-        <v>11.58592751147942</v>
+        <v>11.34263041259995</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>19.41627649622693</v>
+        <v>17.70531378390807</v>
       </c>
     </row>
     <row r="77">
@@ -4804,25 +4660,25 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>9.290631264491166</v>
+        <v>9.289206683320749</v>
       </c>
       <c r="L77" t="n">
         <v>12.83564883207368</v>
       </c>
       <c r="M77" t="n">
-        <v>14.90065600322594</v>
+        <v>12.41804037237105</v>
       </c>
       <c r="N77" t="n">
-        <v>8.655508037001059</v>
+        <v>10.23143391066543</v>
       </c>
       <c r="O77" t="n">
-        <v>11.7780820201135</v>
+        <v>11.32473714151824</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>21.11931935415714</v>
+        <v>17.9741960697253</v>
       </c>
     </row>
     <row r="78">
@@ -4863,25 +4719,25 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>9.301046132712429</v>
+        <v>9.305111203703676</v>
       </c>
       <c r="L78" t="n">
         <v>12.89689920223255</v>
       </c>
       <c r="M78" t="n">
-        <v>14.90065600322594</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="N78" t="n">
-        <v>8.655508037001059</v>
+        <v>10.23143391066543</v>
       </c>
       <c r="O78" t="n">
-        <v>11.7780820201135</v>
+        <v>11.42189396035486</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>21.03089351195738</v>
+        <v>18.53267736505425</v>
       </c>
     </row>
     <row r="79">
@@ -4922,25 +4778,25 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>9.452446335487469</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="L79" t="n">
         <v>13.12043096033579</v>
       </c>
       <c r="M79" t="n">
-        <v>15.10789666146953</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="N79" t="n">
-        <v>8.858023257647872</v>
+        <v>10.15088300892058</v>
       </c>
       <c r="O79" t="n">
-        <v>11.9829599595587</v>
+        <v>11.38161850948243</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>21.11760059794461</v>
+        <v>16.84881589534818</v>
       </c>
     </row>
     <row r="80">
@@ -4981,25 +4837,25 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>9.661749357520293</v>
+        <v>9.671360125421126</v>
       </c>
       <c r="L80" t="n">
         <v>13.45362454391749</v>
       </c>
       <c r="M80" t="n">
-        <v>15.28683754312319</v>
+        <v>12.89114719647669</v>
       </c>
       <c r="N80" t="n">
-        <v>9.152459961658085</v>
+        <v>10.27903163951837</v>
       </c>
       <c r="O80" t="n">
-        <v>12.21964875239064</v>
+        <v>11.58508941799753</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>20.93267528962255</v>
+        <v>16.5188996263025</v>
       </c>
     </row>
     <row r="81">
@@ -5040,25 +4896,25 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>9.737462158199968</v>
+        <v>9.713089998084643</v>
       </c>
       <c r="L81" t="n">
         <v>13.59302364246072</v>
       </c>
       <c r="M81" t="n">
-        <v>15.45586864838683</v>
+        <v>13.08601325120547</v>
       </c>
       <c r="N81" t="n">
-        <v>9.158723808345748</v>
+        <v>10.35214190465377</v>
       </c>
       <c r="O81" t="n">
-        <v>12.30729622836629</v>
+        <v>11.71907757792962</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>20.88057378714326</v>
+        <v>17.11728219653421</v>
       </c>
     </row>
     <row r="82">
@@ -5099,25 +4955,25 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>9.809590006987829</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="L82" t="n">
         <v>13.80479510574496</v>
       </c>
       <c r="M82" t="n">
-        <v>15.45586864838683</v>
+        <v>13.1112961343127</v>
       </c>
       <c r="N82" t="n">
-        <v>9.153048952007417</v>
+        <v>10.55296270291239</v>
       </c>
       <c r="O82" t="n">
-        <v>12.30445880019712</v>
+        <v>11.83212941861254</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>20.27613594162571</v>
+        <v>17.06882276950389</v>
       </c>
     </row>
     <row r="83">
@@ -5158,25 +5014,25 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>9.807131585129085</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="L83" t="n">
         <v>13.82508927942303</v>
       </c>
       <c r="M83" t="n">
-        <v>15.45586864838683</v>
+        <v>13.1112961343127</v>
       </c>
       <c r="N83" t="n">
-        <v>9.153048952007417</v>
+        <v>10.55296270291239</v>
       </c>
       <c r="O83" t="n">
-        <v>12.30445880019712</v>
+        <v>11.83212941861254</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>20.296115868404</v>
+        <v>17.06882276950389</v>
       </c>
     </row>
     <row r="84">
@@ -5217,25 +5073,25 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>10.03578416659066</v>
+        <v>10.04075472918658</v>
       </c>
       <c r="L84" t="n">
         <v>14.23712749276255</v>
       </c>
       <c r="M84" t="n">
-        <v>50.66302055048502</v>
+        <v>12.82287865109407</v>
       </c>
       <c r="N84" t="n">
-        <v>9.403867914857166</v>
+        <v>10.84256885912033</v>
       </c>
       <c r="O84" t="n">
-        <v>30.03344423267109</v>
+        <v>11.8327237551072</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>66.58463781628647</v>
+        <v>15.14418035109769</v>
       </c>
     </row>
     <row r="85">
@@ -5276,25 +5132,25 @@
         <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>10.12549314622187</v>
+        <v>10.14534989254991</v>
       </c>
       <c r="L85" t="n">
         <v>14.31052470761553</v>
       </c>
       <c r="M85" t="n">
-        <v>50.66302055048502</v>
+        <v>12.82287865109407</v>
       </c>
       <c r="N85" t="n">
-        <v>9.403867914857166</v>
+        <v>10.9287005537623</v>
       </c>
       <c r="O85" t="n">
-        <v>30.03344423267109</v>
+        <v>11.87578960242818</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>66.28594087385048</v>
+        <v>14.57115499523891</v>
       </c>
     </row>
     <row r="86">
@@ -5335,25 +5191,25 @@
         <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>10.57589925462877</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="L86" t="n">
         <v>14.74353796333773</v>
       </c>
       <c r="M86" t="n">
-        <v>27.5466963351074</v>
+        <v>12.71927945377958</v>
       </c>
       <c r="N86" t="n">
-        <v>9.051605715933476</v>
+        <v>10.96875577444526</v>
       </c>
       <c r="O86" t="n">
-        <v>18.29915102552044</v>
+        <v>11.84401761411242</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>42.20551959006531</v>
+        <v>10.6850312711432</v>
       </c>
     </row>
     <row r="87">
@@ -5394,25 +5250,25 @@
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>10.60268682414666</v>
+        <v>10.60555613158018</v>
       </c>
       <c r="L87" t="n">
         <v>14.8340861481951</v>
       </c>
       <c r="M87" t="n">
-        <v>27.5466963351074</v>
+        <v>12.77031387086443</v>
       </c>
       <c r="N87" t="n">
-        <v>9.049780946629296</v>
+        <v>10.95155561779406</v>
       </c>
       <c r="O87" t="n">
-        <v>18.29823864086835</v>
+        <v>11.86093474432925</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>42.05624359676889</v>
+        <v>10.58414568336843</v>
       </c>
     </row>
     <row r="88">
@@ -5453,25 +5309,25 @@
         <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>10.62312997770562</v>
+        <v>10.6077046424083</v>
       </c>
       <c r="L88" t="n">
         <v>14.89742045933084</v>
       </c>
       <c r="M88" t="n">
-        <v>27.5466963351074</v>
+        <v>12.77031387086443</v>
       </c>
       <c r="N88" t="n">
-        <v>8.797053500090465</v>
+        <v>10.95155561779406</v>
       </c>
       <c r="O88" t="n">
-        <v>18.17187491759893</v>
+        <v>11.86093474432925</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>41.54081499087674</v>
+        <v>10.56603150540157</v>
       </c>
     </row>
     <row r="89">
@@ -5512,25 +5368,25 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>10.62248024777271</v>
+        <v>10.62865290898554</v>
       </c>
       <c r="L89" t="n">
         <v>15.06944800949407</v>
       </c>
       <c r="M89" t="n">
-        <v>25.49347212687086</v>
+        <v>12.95485717835137</v>
       </c>
       <c r="N89" t="n">
-        <v>8.679703519346106</v>
+        <v>11.13825635405057</v>
       </c>
       <c r="O89" t="n">
-        <v>17.08658782310848</v>
+        <v>12.04655676620097</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>37.8314713403076</v>
+        <v>11.77020027161326</v>
       </c>
     </row>
     <row r="90">
@@ -5571,25 +5427,25 @@
         <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>10.87806600786918</v>
+        <v>10.88520124779484</v>
       </c>
       <c r="L90" t="n">
         <v>15.45898957480362</v>
       </c>
       <c r="M90" t="n">
-        <v>21.33836097537404</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="N90" t="n">
-        <v>8.560910589123965</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="O90" t="n">
-        <v>14.949635782249</v>
+        <v>12.68974774034431</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>27.23524394630641</v>
+        <v>14.22050721159971</v>
       </c>
     </row>
     <row r="91">
@@ -5630,25 +5486,25 @@
         <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>10.92162235687036</v>
+        <v>10.92709848806466</v>
       </c>
       <c r="L91" t="n">
         <v>15.55704238947585</v>
       </c>
       <c r="M91" t="n">
-        <v>21.33836097537404</v>
+        <v>13.75403391875815</v>
       </c>
       <c r="N91" t="n">
-        <v>8.614390892598811</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="O91" t="n">
-        <v>14.97637593398643</v>
+        <v>12.91821418477252</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>27.07433089946991</v>
+        <v>15.41324263732136</v>
       </c>
     </row>
     <row r="92">
@@ -5689,25 +5545,25 @@
         <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>10.95616069257222</v>
+        <v>10.96189869435236</v>
       </c>
       <c r="L92" t="n">
         <v>15.62762686431093</v>
       </c>
       <c r="M92" t="n">
-        <v>21.36069899557773</v>
+        <v>13.75403391875815</v>
       </c>
       <c r="N92" t="n">
-        <v>8.671060242963611</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="O92" t="n">
-        <v>15.01587961927067</v>
+        <v>12.91821418477252</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>27.03617123760371</v>
+        <v>15.14385396029571</v>
       </c>
     </row>
     <row r="93">
@@ -5748,25 +5604,25 @@
         <v>6</v>
       </c>
       <c r="K93" t="n">
-        <v>11.00900355804066</v>
+        <v>11.01112865213726</v>
       </c>
       <c r="L93" t="n">
         <v>15.81963263866668</v>
       </c>
       <c r="M93" t="n">
-        <v>23.60395345894496</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="N93" t="n">
-        <v>8.736947290759135</v>
+        <v>12.77050304400545</v>
       </c>
       <c r="O93" t="n">
-        <v>16.17045037485205</v>
+        <v>13.39708190676929</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>31.91900471021118</v>
+        <v>17.80949964504175</v>
       </c>
     </row>
     <row r="94">
@@ -5807,25 +5663,25 @@
         <v>6</v>
       </c>
       <c r="K94" t="n">
-        <v>11.01773536723862</v>
+        <v>11.018354095561</v>
       </c>
       <c r="L94" t="n">
         <v>15.9889660704432</v>
       </c>
       <c r="M94" t="n">
-        <v>30.32524846705273</v>
+        <v>14.26268479452115</v>
       </c>
       <c r="N94" t="n">
-        <v>8.899453321332752</v>
+        <v>13.02315010602378</v>
       </c>
       <c r="O94" t="n">
-        <v>19.61235089419274</v>
+        <v>13.64291745027246</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>43.82246459550654</v>
+        <v>19.237552116531</v>
       </c>
     </row>
     <row r="95">
@@ -5866,25 +5722,25 @@
         <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>11.01276194340502</v>
+        <v>11.00953264575653</v>
       </c>
       <c r="L95" t="n">
         <v>16.08415780924089</v>
       </c>
       <c r="M95" t="n">
-        <v>30.32524846705273</v>
+        <v>14.26268479452115</v>
       </c>
       <c r="N95" t="n">
-        <v>8.976878747685555</v>
+        <v>13.21812533502401</v>
       </c>
       <c r="O95" t="n">
-        <v>19.65106360736914</v>
+        <v>13.74040506477258</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>43.95844335227106</v>
+        <v>19.87475919481747</v>
       </c>
     </row>
     <row r="96">
@@ -5925,25 +5781,25 @@
         <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>10.91014021015967</v>
+        <v>10.89968555114491</v>
       </c>
       <c r="L96" t="n">
         <v>16.28754364363316</v>
       </c>
       <c r="M96" t="n">
-        <v>33.1118269799849</v>
+        <v>14.35993720530086</v>
       </c>
       <c r="N96" t="n">
-        <v>9.070594825751041</v>
+        <v>13.537726437254</v>
       </c>
       <c r="O96" t="n">
-        <v>21.09121090286797</v>
+        <v>13.94883182127743</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>48.2716271701777</v>
+        <v>21.8595098801132</v>
       </c>
     </row>
     <row r="97">
@@ -5984,25 +5840,25 @@
         <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>10.75714398709465</v>
+        <v>10.74641774112814</v>
       </c>
       <c r="L97" t="n">
         <v>16.44874116728098</v>
       </c>
       <c r="M97" t="n">
-        <v>93.43501340024444</v>
+        <v>14.35993720530086</v>
       </c>
       <c r="N97" t="n">
-        <v>9.549278556066488</v>
+        <v>13.537726437254</v>
       </c>
       <c r="O97" t="n">
-        <v>51.49214597815546</v>
+        <v>13.94883182127743</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>79.10915580861952</v>
+        <v>22.95829587151776</v>
       </c>
     </row>
     <row r="98">
@@ -6043,25 +5899,25 @@
         <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>10.53712094521892</v>
+        <v>10.53428444199073</v>
       </c>
       <c r="L98" t="n">
         <v>16.65372339564686</v>
       </c>
       <c r="M98" t="n">
-        <v>29.05532579013986</v>
+        <v>14.39231959267601</v>
       </c>
       <c r="N98" t="n">
-        <v>9.549278556066488</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="O98" t="n">
-        <v>19.30230217310317</v>
+        <v>13.91533921505495</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>45.41003010562187</v>
+        <v>24.297321975495</v>
       </c>
     </row>
     <row r="99">
@@ -6102,25 +5958,25 @@
         <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>10.38432375970871</v>
+        <v>10.35174796601055</v>
       </c>
       <c r="L99" t="n">
         <v>16.74375365453705</v>
       </c>
       <c r="M99" t="n">
-        <v>10.60692062922534</v>
+        <v>14.39231959267601</v>
       </c>
       <c r="N99" t="n">
-        <v>9.549278556066488</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="O99" t="n">
-        <v>10.07809959264591</v>
+        <v>13.91533921505495</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>-3.038511023310919</v>
+        <v>25.60908644748639</v>
       </c>
     </row>
     <row r="100">
@@ -6161,25 +6017,25 @@
         <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>10.11688682207371</v>
+        <v>10.0797334699099</v>
       </c>
       <c r="L100" t="n">
         <v>16.89900311806041</v>
       </c>
       <c r="M100" t="n">
-        <v>10.24700477381645</v>
+        <v>14.34250198872172</v>
       </c>
       <c r="N100" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O100" t="n">
-        <v>10.10087992834231</v>
+        <v>13.60650048088719</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>-0.1584702901624269</v>
+        <v>25.91972135620972</v>
       </c>
     </row>
     <row r="101">
@@ -6220,25 +6076,25 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>10.11688682207371</v>
+        <v>10.0797334699099</v>
       </c>
       <c r="L101" t="n">
         <v>16.89963155976754</v>
       </c>
       <c r="M101" t="n">
-        <v>10.24700477381645</v>
+        <v>14.34250198872172</v>
       </c>
       <c r="N101" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O101" t="n">
-        <v>10.10087992834231</v>
+        <v>13.60650048088719</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>-0.1584702901624269</v>
+        <v>25.91972135620972</v>
       </c>
     </row>
     <row r="102">
@@ -6279,25 +6135,25 @@
         <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>9.579029976242865</v>
+        <v>9.547526235149299</v>
       </c>
       <c r="L102" t="n">
         <v>17.0525042873831</v>
       </c>
       <c r="M102" t="n">
-        <v>9.761777786710743</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="N102" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O102" t="n">
-        <v>9.858266434789449</v>
+        <v>13.60406477246876</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.83251077046538</v>
+        <v>29.81857705888674</v>
       </c>
     </row>
     <row r="103">
@@ -6338,25 +6194,25 @@
         <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>9.579029976242865</v>
+        <v>9.547526235149299</v>
       </c>
       <c r="L103" t="n">
         <v>17.05374072015774</v>
       </c>
       <c r="M103" t="n">
-        <v>9.761777786710743</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="N103" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O103" t="n">
-        <v>9.858266434789449</v>
+        <v>13.60406477246876</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.83251077046538</v>
+        <v>29.81857705888674</v>
       </c>
     </row>
     <row r="104">
@@ -6397,25 +6253,25 @@
         <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>9.552229142031393</v>
+        <v>9.515191599918353</v>
       </c>
       <c r="L104" t="n">
         <v>17.0977939679632</v>
       </c>
       <c r="M104" t="n">
-        <v>9.761777786710743</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="N104" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O104" t="n">
-        <v>9.858266434789449</v>
+        <v>13.60406477246876</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.104372303005143</v>
+        <v>30.05626069074053</v>
       </c>
     </row>
     <row r="105">
@@ -6456,25 +6312,25 @@
         <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>9.337125357350384</v>
+        <v>9.515191599918353</v>
       </c>
       <c r="L105" t="n">
         <v>17.11128263392759</v>
       </c>
       <c r="M105" t="n">
-        <v>9.761777786710743</v>
+        <v>14.33763057188486</v>
       </c>
       <c r="N105" t="n">
-        <v>9.954755082868157</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="O105" t="n">
-        <v>9.858266434789449</v>
+        <v>13.60406477246876</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.286335897759653</v>
+        <v>30.05626069074053</v>
       </c>
     </row>
     <row r="106">
@@ -6515,25 +6371,25 @@
         <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>8.794782428856642</v>
+        <v>8.778468627187005</v>
       </c>
       <c r="L106" t="n">
         <v>17.43401400622019</v>
       </c>
       <c r="M106" t="n">
-        <v>9.33637179119815</v>
+        <v>14.46958771214976</v>
       </c>
       <c r="N106" t="n">
-        <v>10.238901419118</v>
+        <v>12.7867235364597</v>
       </c>
       <c r="O106" t="n">
-        <v>9.787636605158077</v>
+        <v>13.62815562430473</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>10.1439623920876</v>
+        <v>35.58579114307072</v>
       </c>
     </row>
     <row r="107">
@@ -6574,25 +6430,25 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>8.704344846279827</v>
+        <v>8.766071098486607</v>
       </c>
       <c r="L107" t="n">
         <v>17.50591847546934</v>
       </c>
       <c r="M107" t="n">
-        <v>9.33637179119815</v>
+        <v>14.46958771214976</v>
       </c>
       <c r="N107" t="n">
-        <v>10.238901419118</v>
+        <v>12.89096747702697</v>
       </c>
       <c r="O107" t="n">
-        <v>9.787636605158077</v>
+        <v>13.68027759458836</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>11.06796055655924</v>
+        <v>35.92183318009362</v>
       </c>
     </row>
     <row r="108">
@@ -6633,25 +6489,25 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>8.655508037001059</v>
+        <v>8.660472291933454</v>
       </c>
       <c r="L108" t="n">
         <v>17.83076878484141</v>
       </c>
       <c r="M108" t="n">
-        <v>9.290631264491166</v>
+        <v>14.88833480134777</v>
       </c>
       <c r="N108" t="n">
-        <v>10.19922334404454</v>
+        <v>13.05682586052934</v>
       </c>
       <c r="O108" t="n">
-        <v>9.744927304267854</v>
+        <v>13.97258033093856</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="n">
-        <v>11.17934729784671</v>
+        <v>38.01808909441625</v>
       </c>
     </row>
     <row r="109">
@@ -6692,25 +6548,25 @@
         <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>8.858023257647872</v>
+        <v>8.87437875450698</v>
       </c>
       <c r="L109" t="n">
         <v>18.14375631363999</v>
       </c>
       <c r="M109" t="n">
-        <v>9.452446335487469</v>
+        <v>15.08131980831518</v>
       </c>
       <c r="N109" t="n">
-        <v>10.14784199584086</v>
+        <v>13.28858676062679</v>
       </c>
       <c r="O109" t="n">
-        <v>9.800144165664165</v>
+        <v>14.18495328447098</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>9.613337233518582</v>
+        <v>37.43808261799332</v>
       </c>
     </row>
     <row r="110">
@@ -6751,25 +6607,25 @@
         <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>8.971438026392272</v>
+        <v>8.973642303512785</v>
       </c>
       <c r="L110" t="n">
         <v>18.27104382963625</v>
       </c>
       <c r="M110" t="n">
-        <v>9.452446335487469</v>
+        <v>15.23824314337372</v>
       </c>
       <c r="N110" t="n">
-        <v>10.1470747339985</v>
+        <v>13.22856214979317</v>
       </c>
       <c r="O110" t="n">
-        <v>9.799760534742985</v>
+        <v>14.23340264658345</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>8.45247703159756</v>
+        <v>36.95363978432242</v>
       </c>
     </row>
     <row r="111">
@@ -6810,25 +6666,25 @@
         <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>9.152459961658085</v>
+        <v>9.158641167072478</v>
       </c>
       <c r="L111" t="n">
         <v>18.54487357086113</v>
       </c>
       <c r="M111" t="n">
-        <v>9.737462158199968</v>
+        <v>15.53738489344973</v>
       </c>
       <c r="N111" t="n">
-        <v>10.33989583046221</v>
+        <v>13.22815891986998</v>
       </c>
       <c r="O111" t="n">
-        <v>10.03867899433109</v>
+        <v>14.38277190665985</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>8.828044339035623</v>
+        <v>36.32214133332931</v>
       </c>
     </row>
     <row r="112">
@@ -6869,25 +6725,25 @@
         <v>6</v>
       </c>
       <c r="K112" t="n">
-        <v>9.158723808345748</v>
+        <v>9.158898762760314</v>
       </c>
       <c r="L112" t="n">
         <v>18.57294010586185</v>
       </c>
       <c r="M112" t="n">
-        <v>9.737462158199968</v>
+        <v>15.53738489344973</v>
       </c>
       <c r="N112" t="n">
-        <v>10.34512600052499</v>
+        <v>13.22815891986998</v>
       </c>
       <c r="O112" t="n">
-        <v>10.04129407936248</v>
+        <v>14.38277190665985</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>8.789407660419446</v>
+        <v>36.32035033163989</v>
       </c>
     </row>
     <row r="113">
@@ -6928,25 +6784,25 @@
         <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>9.153048952007417</v>
+        <v>9.151724631834414</v>
       </c>
       <c r="L113" t="n">
         <v>18.82084922067822</v>
       </c>
       <c r="M113" t="n">
-        <v>9.807131585129085</v>
+        <v>15.53738489344973</v>
       </c>
       <c r="N113" t="n">
-        <v>10.54442709905314</v>
+        <v>12.53041601577564</v>
       </c>
       <c r="O113" t="n">
-        <v>10.17577934209111</v>
+        <v>14.03390045461269</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>10.05063450868349</v>
+        <v>34.78844558266474</v>
       </c>
     </row>
     <row r="114">
@@ -6987,25 +6843,25 @@
         <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>9.256091506980455</v>
+        <v>9.205402671033942</v>
       </c>
       <c r="L114" t="n">
         <v>19.02764744690028</v>
       </c>
       <c r="M114" t="n">
-        <v>9.807131585129085</v>
+        <v>41.85527415873189</v>
       </c>
       <c r="N114" t="n">
-        <v>10.69190504591853</v>
+        <v>12.29751099175077</v>
       </c>
       <c r="O114" t="n">
-        <v>10.24951831552381</v>
+        <v>27.07639257524134</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>9.692424345822371</v>
+        <v>66.00210812628205</v>
       </c>
     </row>
     <row r="115">
@@ -7046,25 +6902,25 @@
         <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>9.403867914857166</v>
+        <v>9.403399618816287</v>
       </c>
       <c r="L115" t="n">
         <v>19.35429029801131</v>
       </c>
       <c r="M115" t="n">
-        <v>10.12549314622187</v>
+        <v>51.03791363001811</v>
       </c>
       <c r="N115" t="n">
-        <v>10.92685448189717</v>
+        <v>12.3111585689887</v>
       </c>
       <c r="O115" t="n">
-        <v>10.52617381405952</v>
+        <v>31.6745360995034</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="n">
-        <v>10.66204984857199</v>
+        <v>70.31243144563777</v>
       </c>
     </row>
     <row r="116">
@@ -7105,25 +6961,25 @@
         <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>9.368423488149045</v>
+        <v>9.399987799230123</v>
       </c>
       <c r="L116" t="n">
         <v>19.42713761877428</v>
       </c>
       <c r="M116" t="n">
-        <v>10.12549314622187</v>
+        <v>70.22101375492795</v>
       </c>
       <c r="N116" t="n">
-        <v>10.92685448189717</v>
+        <v>12.3111585689887</v>
       </c>
       <c r="O116" t="n">
-        <v>10.52617381405952</v>
+        <v>41.26608616195833</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>10.99877644395444</v>
+        <v>77.22103384765472</v>
       </c>
     </row>
     <row r="117">
@@ -7164,25 +7020,25 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>9.268971225409532</v>
+        <v>9.250192540660322</v>
       </c>
       <c r="L117" t="n">
         <v>19.54842137126722</v>
       </c>
       <c r="M117" t="n">
-        <v>10.57589925462877</v>
+        <v>70.22101375492795</v>
       </c>
       <c r="N117" t="n">
-        <v>10.94563504361946</v>
+        <v>12.35319462240552</v>
       </c>
       <c r="O117" t="n">
-        <v>10.76076714912411</v>
+        <v>41.28710418866674</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>13.86328598176208</v>
+        <v>77.59544360779003</v>
       </c>
     </row>
     <row r="118">
@@ -7223,25 +7079,25 @@
         <v>6</v>
       </c>
       <c r="K118" t="n">
-        <v>9.159228079297097</v>
+        <v>9.141918112841262</v>
       </c>
       <c r="L118" t="n">
         <v>19.63959269337549</v>
       </c>
       <c r="M118" t="n">
-        <v>10.57589925462877</v>
+        <v>70.22101375492795</v>
       </c>
       <c r="N118" t="n">
-        <v>10.9708481273363</v>
+        <v>12.35319462240552</v>
       </c>
       <c r="O118" t="n">
-        <v>10.77337369098254</v>
+        <v>41.28710418866674</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>14.98273111083579</v>
+        <v>77.8576911786642</v>
       </c>
     </row>
     <row r="119">
@@ -7282,25 +7138,25 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>9.051605715933476</v>
+        <v>9.126831340801603</v>
       </c>
       <c r="L119" t="n">
         <v>19.73230934132484</v>
       </c>
       <c r="M119" t="n">
-        <v>10.57589925462877</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="N119" t="n">
-        <v>10.95402348740476</v>
+        <v>12.35342338176835</v>
       </c>
       <c r="O119" t="n">
-        <v>10.76496137101677</v>
+        <v>20.24634190954897</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>15.9160409037442</v>
+        <v>54.92108460098151</v>
       </c>
     </row>
     <row r="120">
@@ -7341,25 +7197,25 @@
         <v>6</v>
       </c>
       <c r="K120" t="n">
-        <v>9.049780946629296</v>
+        <v>9.032940356461713</v>
       </c>
       <c r="L120" t="n">
         <v>19.7675119737061</v>
       </c>
       <c r="M120" t="n">
-        <v>10.57589925462877</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="N120" t="n">
-        <v>10.95402348740476</v>
+        <v>12.35342338176835</v>
       </c>
       <c r="O120" t="n">
-        <v>10.76496137101677</v>
+        <v>20.24634190954897</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>15.93299191026701</v>
+        <v>55.3848275564218</v>
       </c>
     </row>
     <row r="121">
@@ -7400,25 +7256,25 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
-        <v>9.049780946629296</v>
+        <v>9.032940356461713</v>
       </c>
       <c r="L121" t="n">
         <v>19.76765368342005</v>
       </c>
       <c r="M121" t="n">
-        <v>10.57589925462877</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="N121" t="n">
-        <v>10.95402348740476</v>
+        <v>12.35342338176835</v>
       </c>
       <c r="O121" t="n">
-        <v>10.76496137101677</v>
+        <v>20.24634190954897</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>15.93299191026701</v>
+        <v>55.3848275564218</v>
       </c>
     </row>
     <row r="122">
@@ -7459,25 +7315,25 @@
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>8.797053500090465</v>
+        <v>8.778672810676495</v>
       </c>
       <c r="L122" t="n">
         <v>19.95551280332359</v>
       </c>
       <c r="M122" t="n">
-        <v>10.62312997770562</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="N122" t="n">
-        <v>11.12657912438668</v>
+        <v>12.50552073045885</v>
       </c>
       <c r="O122" t="n">
-        <v>10.87485455104615</v>
+        <v>20.32239058389422</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>19.10647210224806</v>
+        <v>56.80295202261432</v>
       </c>
     </row>
     <row r="123">
@@ -7518,25 +7374,25 @@
         <v>6</v>
       </c>
       <c r="K123" t="n">
-        <v>8.797053500090465</v>
+        <v>8.778672810676495</v>
       </c>
       <c r="L123" t="n">
         <v>19.96498624128395</v>
       </c>
       <c r="M123" t="n">
-        <v>10.62312997770562</v>
+        <v>28.13926043732958</v>
       </c>
       <c r="N123" t="n">
-        <v>11.12657912438668</v>
+        <v>12.50552073045885</v>
       </c>
       <c r="O123" t="n">
-        <v>10.87485455104615</v>
+        <v>20.32239058389422</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>19.10647210224806</v>
+        <v>56.80295202261432</v>
       </c>
     </row>
     <row r="124">
@@ -7577,25 +7433,25 @@
         <v>6</v>
       </c>
       <c r="K124" t="n">
-        <v>8.679703519346106</v>
+        <v>8.672861443756478</v>
       </c>
       <c r="L124" t="n">
         <v>20.07583611076447</v>
       </c>
       <c r="M124" t="n">
-        <v>10.62248024777271</v>
+        <v>25.80032314541072</v>
       </c>
       <c r="N124" t="n">
-        <v>11.12657912438668</v>
+        <v>12.50552073045885</v>
       </c>
       <c r="O124" t="n">
-        <v>10.8745296860797</v>
+        <v>19.15292193793479</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>20.1831824464386</v>
+        <v>54.71781552777711</v>
       </c>
     </row>
     <row r="125">
@@ -7636,25 +7492,25 @@
         <v>6</v>
       </c>
       <c r="K125" t="n">
-        <v>8.671066277014619</v>
+        <v>8.670969426295731</v>
       </c>
       <c r="L125" t="n">
         <v>20.0823564584345</v>
       </c>
       <c r="M125" t="n">
-        <v>10.62248024777271</v>
+        <v>25.80032314541072</v>
       </c>
       <c r="N125" t="n">
-        <v>11.12657912438668</v>
+        <v>12.50552073045885</v>
       </c>
       <c r="O125" t="n">
-        <v>10.8745296860797</v>
+        <v>19.15292193793479</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>20.26260879940118</v>
+        <v>54.72769400724295</v>
       </c>
     </row>
     <row r="126">
@@ -7695,25 +7551,25 @@
         <v>6</v>
       </c>
       <c r="K126" t="n">
-        <v>8.527369824730963</v>
+        <v>8.533079617107587</v>
       </c>
       <c r="L126" t="n">
         <v>20.35524231361114</v>
       </c>
       <c r="M126" t="n">
-        <v>10.87806600786918</v>
+        <v>25.67335572679642</v>
       </c>
       <c r="N126" t="n">
-        <v>11.14795892046014</v>
+        <v>12.64447152506395</v>
       </c>
       <c r="O126" t="n">
-        <v>11.01301246416466</v>
+        <v>19.15891362593019</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>22.57005199550758</v>
+        <v>55.46156852255606</v>
       </c>
     </row>
     <row r="127">
@@ -7754,25 +7610,25 @@
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>8.527369824730963</v>
+        <v>8.533079617107587</v>
       </c>
       <c r="L127" t="n">
         <v>20.36131897189755</v>
       </c>
       <c r="M127" t="n">
-        <v>10.87806600786918</v>
+        <v>22.39575428021364</v>
       </c>
       <c r="N127" t="n">
-        <v>11.14795892046014</v>
+        <v>12.64447152506395</v>
       </c>
       <c r="O127" t="n">
-        <v>11.01301246416466</v>
+        <v>17.5201129026388</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>22.57005199550758</v>
+        <v>51.29552152701953</v>
       </c>
     </row>
     <row r="128">
@@ -7813,25 +7669,25 @@
         <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>8.560910589123965</v>
+        <v>8.563832986313626</v>
       </c>
       <c r="L128" t="n">
         <v>20.48066051718489</v>
       </c>
       <c r="M128" t="n">
-        <v>10.87806600786918</v>
+        <v>22.39575428021364</v>
       </c>
       <c r="N128" t="n">
-        <v>12.05835100310014</v>
+        <v>12.64447152506395</v>
       </c>
       <c r="O128" t="n">
-        <v>11.46820850548466</v>
+        <v>17.5201129026388</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>25.35093353918601</v>
+        <v>51.11998972892589</v>
       </c>
     </row>
     <row r="129">
@@ -7872,25 +7728,25 @@
         <v>6</v>
       </c>
       <c r="K129" t="n">
-        <v>8.614390892598811</v>
+        <v>8.618593561821877</v>
       </c>
       <c r="L129" t="n">
         <v>20.54271324726493</v>
       </c>
       <c r="M129" t="n">
-        <v>10.92162235687036</v>
+        <v>22.39575428021364</v>
       </c>
       <c r="N129" t="n">
-        <v>12.05835100310014</v>
+        <v>12.74559832073476</v>
       </c>
       <c r="O129" t="n">
-        <v>11.48998667998525</v>
+        <v>17.5706763004742</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
       </c>
       <c r="Q129" t="n">
-        <v>25.02697233231371</v>
+        <v>50.94899357067276</v>
       </c>
     </row>
     <row r="130">
@@ -7931,25 +7787,25 @@
         <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>8.614390892598811</v>
+        <v>8.618593561821877</v>
       </c>
       <c r="L130" t="n">
         <v>20.54321568793345</v>
       </c>
       <c r="M130" t="n">
-        <v>10.92162235687036</v>
+        <v>22.39575428021364</v>
       </c>
       <c r="N130" t="n">
-        <v>12.05835100310014</v>
+        <v>12.74559832073476</v>
       </c>
       <c r="O130" t="n">
-        <v>11.48998667998525</v>
+        <v>17.5706763004742</v>
       </c>
       <c r="P130" t="b">
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>25.02697233231371</v>
+        <v>50.94899357067276</v>
       </c>
     </row>
     <row r="131">
@@ -7990,25 +7846,25 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
-        <v>8.671060242963611</v>
+        <v>8.670332350741491</v>
       </c>
       <c r="L131" t="n">
         <v>20.6394566023131</v>
       </c>
       <c r="M131" t="n">
-        <v>10.95616069257222</v>
+        <v>22.40658457261621</v>
       </c>
       <c r="N131" t="n">
-        <v>12.05835100310014</v>
+        <v>12.74559832073476</v>
       </c>
       <c r="O131" t="n">
-        <v>11.50725584783618</v>
+        <v>17.57609144667548</v>
       </c>
       <c r="P131" t="b">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>24.64701960551163</v>
+        <v>50.6697357768841</v>
       </c>
     </row>
     <row r="132">
@@ -8049,25 +7905,25 @@
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>8.736947290759135</v>
+        <v>8.737214268524154</v>
       </c>
       <c r="L132" t="n">
         <v>20.81667772931799</v>
       </c>
       <c r="M132" t="n">
-        <v>11.00900355804066</v>
+        <v>22.66819578486057</v>
       </c>
       <c r="N132" t="n">
-        <v>12.7514670715484</v>
+        <v>12.82934323440308</v>
       </c>
       <c r="O132" t="n">
-        <v>11.88023531479453</v>
+        <v>17.74876950963182</v>
       </c>
       <c r="P132" t="b">
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>26.45812932780076</v>
+        <v>50.77284504831346</v>
       </c>
     </row>
     <row r="133">
@@ -8108,25 +7964,25 @@
         <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>8.899453321332752</v>
+        <v>8.908018607468405</v>
       </c>
       <c r="L133" t="n">
         <v>21.02206787277562</v>
       </c>
       <c r="M133" t="n">
-        <v>11.01773536723862</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="N133" t="n">
-        <v>12.99740495364647</v>
+        <v>12.91446486725206</v>
       </c>
       <c r="O133" t="n">
-        <v>12.00757016044254</v>
+        <v>20.08079119727815</v>
       </c>
       <c r="P133" t="b">
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>25.88464441664559</v>
+        <v>55.63910545180192</v>
       </c>
     </row>
     <row r="134">
@@ -8167,25 +8023,25 @@
         <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>8.976878747685555</v>
+        <v>8.988453081253281</v>
       </c>
       <c r="L134" t="n">
         <v>21.04333135668024</v>
       </c>
       <c r="M134" t="n">
-        <v>11.01276194340502</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="N134" t="n">
-        <v>12.99740495364647</v>
+        <v>12.91446486725206</v>
       </c>
       <c r="O134" t="n">
-        <v>12.00508344852575</v>
+        <v>20.08079119727815</v>
       </c>
       <c r="P134" t="b">
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>25.22435361506848</v>
+        <v>55.23855114597467</v>
       </c>
     </row>
     <row r="135">
@@ -8226,25 +8082,25 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>9.070594825751041</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="L135" t="n">
         <v>21.16755097601469</v>
       </c>
       <c r="M135" t="n">
-        <v>11.01276194340502</v>
+        <v>27.24711752730424</v>
       </c>
       <c r="N135" t="n">
-        <v>13.38196974327161</v>
+        <v>12.90839304015632</v>
       </c>
       <c r="O135" t="n">
-        <v>12.19736584333831</v>
+        <v>20.07775528373028</v>
       </c>
       <c r="P135" t="b">
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>25.63480556168596</v>
+        <v>54.76457851323288</v>
       </c>
     </row>
     <row r="136">
@@ -8285,25 +8141,25 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9.549278556066488</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="L136" t="n">
         <v>21.63813487811026</v>
       </c>
       <c r="M136" t="n">
-        <v>10.53712094521892</v>
+        <v>28.56331160274965</v>
       </c>
       <c r="N136" t="n">
-        <v>13.52513424291054</v>
+        <v>12.73965880607229</v>
       </c>
       <c r="O136" t="n">
-        <v>12.03112759406473</v>
+        <v>20.65148520441097</v>
       </c>
       <c r="P136" t="b">
         <v>1</v>
       </c>
       <c r="Q136" t="n">
-        <v>20.62856551552659</v>
+        <v>54.03135716528912</v>
       </c>
     </row>
     <row r="137">
@@ -8344,25 +8200,25 @@
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>9.549278556066488</v>
+        <v>9.562461236943456</v>
       </c>
       <c r="L137" t="n">
         <v>21.66369351945806</v>
       </c>
       <c r="M137" t="n">
-        <v>10.53712094521892</v>
+        <v>28.56331160274965</v>
       </c>
       <c r="N137" t="n">
-        <v>13.45373608070102</v>
+        <v>12.66848637001136</v>
       </c>
       <c r="O137" t="n">
-        <v>11.99542851295997</v>
+        <v>20.61589898638051</v>
       </c>
       <c r="P137" t="b">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>20.3923515883625</v>
+        <v>53.61608415300876</v>
       </c>
     </row>
     <row r="138">
@@ -8403,25 +8259,25 @@
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>9.954755082868157</v>
+        <v>9.977092619200015</v>
       </c>
       <c r="L138" t="n">
         <v>22.07285259496778</v>
       </c>
       <c r="M138" t="n">
-        <v>9.579029976242865</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="N138" t="n">
-        <v>12.87687986559452</v>
+        <v>12.27482045438042</v>
       </c>
       <c r="O138" t="n">
-        <v>11.22795492091869</v>
+        <v>11.00863411843088</v>
       </c>
       <c r="P138" t="b">
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>11.33955245650703</v>
+        <v>9.37029506234418</v>
       </c>
     </row>
     <row r="139">
@@ -8462,25 +8318,25 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>10.06934780780029</v>
+        <v>10.08724170276781</v>
       </c>
       <c r="L139" t="n">
         <v>22.15715011866932</v>
       </c>
       <c r="M139" t="n">
-        <v>9.337125357350384</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="N139" t="n">
-        <v>12.87687986559452</v>
+        <v>12.27482045438042</v>
       </c>
       <c r="O139" t="n">
-        <v>11.10700261147245</v>
+        <v>11.00863411843088</v>
       </c>
       <c r="P139" t="b">
         <v>1</v>
       </c>
       <c r="Q139" t="n">
-        <v>9.342347705945143</v>
+        <v>8.369725124395377</v>
       </c>
     </row>
     <row r="140">
@@ -8521,25 +8377,25 @@
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>10.06934780780029</v>
+        <v>10.08724170276781</v>
       </c>
       <c r="L140" t="n">
         <v>22.15748337565279</v>
       </c>
       <c r="M140" t="n">
-        <v>9.337125357350384</v>
+        <v>9.74244778248134</v>
       </c>
       <c r="N140" t="n">
-        <v>12.87687986559452</v>
+        <v>12.27482045438042</v>
       </c>
       <c r="O140" t="n">
-        <v>11.10700261147245</v>
+        <v>11.00863411843088</v>
       </c>
       <c r="P140" t="b">
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>9.342347705945143</v>
+        <v>8.369725124395377</v>
       </c>
     </row>
     <row r="141">
@@ -8580,25 +8436,25 @@
         <v>6</v>
       </c>
       <c r="K141" t="n">
-        <v>10.238901419118</v>
+        <v>10.23949170105669</v>
       </c>
       <c r="L141" t="n">
         <v>22.39987799650586</v>
       </c>
       <c r="M141" t="n">
-        <v>8.794782428856642</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="N141" t="n">
-        <v>12.78203660848068</v>
+        <v>12.27482045438042</v>
       </c>
       <c r="O141" t="n">
-        <v>10.78840951866866</v>
+        <v>10.80460128054028</v>
       </c>
       <c r="P141" t="b">
         <v>1</v>
       </c>
       <c r="Q141" t="n">
-        <v>5.093504270483717</v>
+        <v>5.230267779537501</v>
       </c>
     </row>
     <row r="142">
@@ -8639,25 +8495,25 @@
         <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>10.238901419118</v>
+        <v>10.23949170105669</v>
       </c>
       <c r="L142" t="n">
         <v>22.42159995864994</v>
       </c>
       <c r="M142" t="n">
-        <v>8.794782428856642</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="N142" t="n">
-        <v>12.78203660848068</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="O142" t="n">
-        <v>10.78840951866866</v>
+        <v>10.61054478687801</v>
       </c>
       <c r="P142" t="b">
         <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>5.093504270483717</v>
+        <v>3.497022002868322</v>
       </c>
     </row>
     <row r="143">
@@ -8698,25 +8554,25 @@
         <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>10.26949459641317</v>
+        <v>10.26722045282886</v>
       </c>
       <c r="L143" t="n">
         <v>22.62473529463472</v>
       </c>
       <c r="M143" t="n">
-        <v>8.704344846279827</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="N143" t="n">
-        <v>12.88732088272113</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="O143" t="n">
-        <v>10.79583286450048</v>
+        <v>10.61054478687801</v>
       </c>
       <c r="P143" t="b">
         <v>1</v>
       </c>
       <c r="Q143" t="n">
-        <v>4.875383628974539</v>
+        <v>3.235689975822365</v>
       </c>
     </row>
     <row r="144">
@@ -8757,25 +8613,25 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>10.26591014938876</v>
+        <v>10.26722045282886</v>
       </c>
       <c r="L144" t="n">
         <v>22.63512122951012</v>
       </c>
       <c r="M144" t="n">
-        <v>8.704344846279827</v>
+        <v>9.334382106700145</v>
       </c>
       <c r="N144" t="n">
-        <v>12.88732088272113</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="O144" t="n">
-        <v>10.79583286450048</v>
+        <v>10.61054478687801</v>
       </c>
       <c r="P144" t="b">
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>4.908585764181639</v>
+        <v>3.235689975822365</v>
       </c>
     </row>
     <row r="145">
@@ -8816,25 +8672,25 @@
         <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>10.19922334404454</v>
+        <v>10.23143391066543</v>
       </c>
       <c r="L145" t="n">
         <v>22.83583681303224</v>
       </c>
       <c r="M145" t="n">
-        <v>8.655508037001059</v>
+        <v>9.289206683320749</v>
       </c>
       <c r="N145" t="n">
-        <v>13.10364382962162</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="O145" t="n">
-        <v>10.87957593331134</v>
+        <v>10.58795707518831</v>
       </c>
       <c r="P145" t="b">
         <v>1</v>
       </c>
       <c r="Q145" t="n">
-        <v>6.253484450470848</v>
+        <v>3.367251699181428</v>
       </c>
     </row>
     <row r="146">
@@ -8875,25 +8731,25 @@
         <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>10.157607343109</v>
+        <v>10.15570606108186</v>
       </c>
       <c r="L146" t="n">
         <v>23.00756852757851</v>
       </c>
       <c r="M146" t="n">
-        <v>8.858023257647872</v>
+        <v>9.305111203703676</v>
       </c>
       <c r="N146" t="n">
-        <v>13.21665282962994</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="O146" t="n">
-        <v>11.0373380436389</v>
+        <v>10.73728042837707</v>
       </c>
       <c r="P146" t="b">
         <v>1</v>
       </c>
       <c r="Q146" t="n">
-        <v>7.970497026109625</v>
+        <v>5.416402888744509</v>
       </c>
     </row>
     <row r="147">
@@ -8934,25 +8790,25 @@
         <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>10.15135689057502</v>
+        <v>10.15088300892058</v>
       </c>
       <c r="L147" t="n">
         <v>23.06798621348663</v>
       </c>
       <c r="M147" t="n">
-        <v>8.858023257647872</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="N147" t="n">
-        <v>13.21665282962994</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="O147" t="n">
-        <v>11.0373380436389</v>
+        <v>10.81670010697967</v>
       </c>
       <c r="P147" t="b">
         <v>1</v>
       </c>
       <c r="Q147" t="n">
-        <v>8.027127098589649</v>
+        <v>6.155454912071145</v>
       </c>
     </row>
     <row r="148">
@@ -8993,25 +8849,25 @@
         <v>6</v>
       </c>
       <c r="K148" t="n">
-        <v>10.14784199584086</v>
+        <v>10.14758974514527</v>
       </c>
       <c r="L148" t="n">
         <v>23.18491569423517</v>
       </c>
       <c r="M148" t="n">
-        <v>8.858023257647872</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="N148" t="n">
-        <v>13.21665282962994</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="O148" t="n">
-        <v>11.0373380436389</v>
+        <v>10.81670010697967</v>
       </c>
       <c r="P148" t="b">
         <v>1</v>
       </c>
       <c r="Q148" t="n">
-        <v>8.058972591771663</v>
+        <v>6.185901016176254</v>
       </c>
     </row>
     <row r="149">
@@ -9052,25 +8908,25 @@
         <v>6</v>
       </c>
       <c r="K149" t="n">
-        <v>10.1470747339985</v>
+        <v>10.14761124577038</v>
       </c>
       <c r="L149" t="n">
         <v>23.25206105753598</v>
       </c>
       <c r="M149" t="n">
-        <v>8.971438026392272</v>
+        <v>9.463950560908867</v>
       </c>
       <c r="N149" t="n">
-        <v>13.21665282962994</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="O149" t="n">
-        <v>11.09404542801111</v>
+        <v>10.81670010697967</v>
       </c>
       <c r="P149" t="b">
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>8.535846550813819</v>
+        <v>6.185702243677349</v>
       </c>
     </row>
     <row r="150">
@@ -9111,25 +8967,25 @@
         <v>6</v>
       </c>
       <c r="K150" t="n">
-        <v>10.26983464027998</v>
+        <v>10.27903163951837</v>
       </c>
       <c r="L150" t="n">
         <v>23.50886552740835</v>
       </c>
       <c r="M150" t="n">
-        <v>9.152459961658085</v>
+        <v>9.671360125421126</v>
       </c>
       <c r="N150" t="n">
-        <v>13.22836695411769</v>
+        <v>12.28702891766755</v>
       </c>
       <c r="O150" t="n">
-        <v>11.19041345788789</v>
+        <v>10.97919452154434</v>
       </c>
       <c r="P150" t="b">
         <v>1</v>
       </c>
       <c r="Q150" t="n">
-        <v>8.226495125245004</v>
+        <v>6.377178951079232</v>
       </c>
     </row>
     <row r="151">
@@ -9170,25 +9026,25 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>10.33989583046221</v>
+        <v>10.35214190465377</v>
       </c>
       <c r="L151" t="n">
         <v>23.55584809282101</v>
       </c>
       <c r="M151" t="n">
-        <v>9.152459961658085</v>
+        <v>9.713089998084643</v>
       </c>
       <c r="N151" t="n">
-        <v>13.22836695411769</v>
+        <v>12.28702891766755</v>
       </c>
       <c r="O151" t="n">
-        <v>11.19041345788789</v>
+        <v>11.0000594578761</v>
       </c>
       <c r="P151" t="b">
         <v>1</v>
       </c>
       <c r="Q151" t="n">
-        <v>7.600412894718966</v>
+        <v>5.890127737067918</v>
       </c>
     </row>
     <row r="152">
@@ -9229,25 +9085,25 @@
         <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>10.34512600052499</v>
+        <v>10.35214190465377</v>
       </c>
       <c r="L152" t="n">
         <v>23.58894008392281</v>
       </c>
       <c r="M152" t="n">
-        <v>9.158723808345748</v>
+        <v>9.713089998084643</v>
       </c>
       <c r="N152" t="n">
-        <v>13.22836695411769</v>
+        <v>12.28702891766755</v>
       </c>
       <c r="O152" t="n">
-        <v>11.19354538123172</v>
+        <v>11.0000594578761</v>
       </c>
       <c r="P152" t="b">
         <v>1</v>
       </c>
       <c r="Q152" t="n">
-        <v>7.579541171372595</v>
+        <v>5.890127737067918</v>
       </c>
     </row>
     <row r="153">
@@ -9288,25 +9144,25 @@
         <v>6</v>
       </c>
       <c r="K153" t="n">
-        <v>10.54442709905314</v>
+        <v>10.55296270291239</v>
       </c>
       <c r="L153" t="n">
         <v>23.83152967282308</v>
       </c>
       <c r="M153" t="n">
-        <v>9.153048952007417</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="N153" t="n">
-        <v>12.54081239321359</v>
+        <v>12.46436863874414</v>
       </c>
       <c r="O153" t="n">
-        <v>10.8469306726105</v>
+        <v>11.13844642851769</v>
       </c>
       <c r="P153" t="b">
         <v>1</v>
       </c>
       <c r="Q153" t="n">
-        <v>2.788840296741402</v>
+        <v>5.256421794212618</v>
       </c>
     </row>
     <row r="154">
@@ -9347,25 +9203,25 @@
         <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>10.61904542555895</v>
+        <v>10.62689904180005</v>
       </c>
       <c r="L154" t="n">
         <v>23.930678152739</v>
       </c>
       <c r="M154" t="n">
-        <v>9.256091506980455</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="N154" t="n">
-        <v>12.54081239321359</v>
+        <v>12.49027804851815</v>
       </c>
       <c r="O154" t="n">
-        <v>10.89845195009702</v>
+        <v>11.15140113340469</v>
       </c>
       <c r="P154" t="b">
         <v>1</v>
       </c>
       <c r="Q154" t="n">
-        <v>2.563726718413284</v>
+        <v>4.703463585696577</v>
       </c>
     </row>
     <row r="155">
@@ -9406,25 +9262,25 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>10.69190504591853</v>
+        <v>10.70087459568568</v>
       </c>
       <c r="L155" t="n">
         <v>24.00777951536901</v>
       </c>
       <c r="M155" t="n">
-        <v>9.256091506980455</v>
+        <v>9.812524218291237</v>
       </c>
       <c r="N155" t="n">
-        <v>12.29943552785324</v>
+        <v>12.49027804851815</v>
       </c>
       <c r="O155" t="n">
-        <v>10.77776351741685</v>
+        <v>11.15140113340469</v>
       </c>
       <c r="P155" t="b">
         <v>1</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.7966260473201925</v>
+        <v>4.040089064408536</v>
       </c>
     </row>
     <row r="156">
@@ -9465,25 +9321,25 @@
         <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>10.75670064819602</v>
+        <v>10.76665165193404</v>
       </c>
       <c r="L156" t="n">
         <v>24.07839113089585</v>
       </c>
       <c r="M156" t="n">
-        <v>9.256091506980455</v>
+        <v>10.04075472918658</v>
       </c>
       <c r="N156" t="n">
-        <v>12.29943552785324</v>
+        <v>12.51606374896549</v>
       </c>
       <c r="O156" t="n">
-        <v>10.77776351741685</v>
+        <v>11.27840923907604</v>
       </c>
       <c r="P156" t="b">
         <v>1</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.1954289420693756</v>
+        <v>4.537497942253399</v>
       </c>
     </row>
     <row r="157">
@@ -9524,25 +9380,25 @@
         <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>10.83306256459373</v>
+        <v>10.84256885912033</v>
       </c>
       <c r="L157" t="n">
         <v>24.15828491916498</v>
       </c>
       <c r="M157" t="n">
-        <v>9.256091506980455</v>
+        <v>10.04075472918658</v>
       </c>
       <c r="N157" t="n">
-        <v>12.2829233494113</v>
+        <v>12.51606374896549</v>
       </c>
       <c r="O157" t="n">
-        <v>10.76950742819588</v>
+        <v>11.27840923907604</v>
       </c>
       <c r="P157" t="b">
         <v>1</v>
       </c>
       <c r="Q157" t="n">
-        <v>-0.590139677432755</v>
+        <v>3.86437812919278</v>
       </c>
     </row>
     <row r="158">
@@ -9583,25 +9439,25 @@
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>10.92685448189717</v>
+        <v>10.9287005537623</v>
       </c>
       <c r="L158" t="n">
         <v>24.39142347189334</v>
       </c>
       <c r="M158" t="n">
-        <v>9.368423488149045</v>
+        <v>10.14534989254991</v>
       </c>
       <c r="N158" t="n">
-        <v>12.30719348999601</v>
+        <v>12.54276937654406</v>
       </c>
       <c r="O158" t="n">
-        <v>10.83780848907253</v>
+        <v>11.34405963454698</v>
       </c>
       <c r="P158" t="b">
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>-0.8216236051266979</v>
+        <v>3.661467712314848</v>
       </c>
     </row>
     <row r="159">
@@ -9642,25 +9498,25 @@
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>10.94563504361946</v>
+        <v>10.94679446313857</v>
       </c>
       <c r="L159" t="n">
         <v>24.52320791350618</v>
       </c>
       <c r="M159" t="n">
-        <v>9.268971225409532</v>
+        <v>10.14534989254991</v>
       </c>
       <c r="N159" t="n">
-        <v>12.30719348999601</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="O159" t="n">
-        <v>10.78808235770277</v>
+        <v>11.36142647354495</v>
       </c>
       <c r="P159" t="b">
         <v>1</v>
       </c>
       <c r="Q159" t="n">
-        <v>-1.460432732089689</v>
+        <v>3.649471405477511</v>
       </c>
     </row>
     <row r="160">
@@ -9701,25 +9557,25 @@
         <v>6</v>
       </c>
       <c r="K160" t="n">
-        <v>10.94563504361946</v>
+        <v>10.94679446313857</v>
       </c>
       <c r="L160" t="n">
         <v>24.5284387189814</v>
       </c>
       <c r="M160" t="n">
-        <v>9.268971225409532</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="N160" t="n">
-        <v>12.30719348999601</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="O160" t="n">
-        <v>10.78808235770277</v>
+        <v>11.57799184141239</v>
       </c>
       <c r="P160" t="b">
         <v>1</v>
       </c>
       <c r="Q160" t="n">
-        <v>-1.460432732089689</v>
+        <v>5.451699974568481</v>
       </c>
     </row>
     <row r="161">
@@ -9760,25 +9616,25 @@
         <v>6</v>
       </c>
       <c r="K161" t="n">
-        <v>10.9708481273363</v>
+        <v>10.97041257937665</v>
       </c>
       <c r="L161" t="n">
         <v>24.66073661779361</v>
       </c>
       <c r="M161" t="n">
-        <v>9.159228079297097</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="N161" t="n">
-        <v>12.35258897367873</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="O161" t="n">
-        <v>10.75590852648791</v>
+        <v>11.57799184141239</v>
       </c>
       <c r="P161" t="b">
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>-1.998339799181692</v>
+        <v>5.247708500385562</v>
       </c>
     </row>
     <row r="162">
@@ -9819,25 +9675,25 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>10.95402348740476</v>
+        <v>10.96875577444526</v>
       </c>
       <c r="L162" t="n">
         <v>24.74876546621858</v>
       </c>
       <c r="M162" t="n">
-        <v>9.051605715933476</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="N162" t="n">
-        <v>12.35296321494364</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="O162" t="n">
-        <v>10.70228446543856</v>
+        <v>11.56912399674058</v>
       </c>
       <c r="P162" t="b">
         <v>1</v>
       </c>
       <c r="Q162" t="n">
-        <v>-2.352198942003025</v>
+        <v>5.189400878272787</v>
       </c>
     </row>
     <row r="163">
@@ -9878,25 +9734,25 @@
         <v>6</v>
       </c>
       <c r="K163" t="n">
-        <v>10.95402348740476</v>
+        <v>10.95155561779406</v>
       </c>
       <c r="L163" t="n">
         <v>24.7532073466283</v>
       </c>
       <c r="M163" t="n">
-        <v>9.049780946629296</v>
+        <v>10.5784806282848</v>
       </c>
       <c r="N163" t="n">
-        <v>12.35296321494364</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="O163" t="n">
-        <v>10.70137208078647</v>
+        <v>11.56912399674058</v>
       </c>
       <c r="P163" t="b">
         <v>1</v>
       </c>
       <c r="Q163" t="n">
-        <v>-2.360925353412457</v>
+        <v>5.338073817175005</v>
       </c>
     </row>
     <row r="164">
@@ -9937,25 +9793,25 @@
         <v>6</v>
       </c>
       <c r="K164" t="n">
-        <v>11.12657912438668</v>
+        <v>11.13825635405057</v>
       </c>
       <c r="L164" t="n">
         <v>25.05436419001699</v>
       </c>
       <c r="M164" t="n">
-        <v>8.679703519346106</v>
+        <v>10.62865290898554</v>
       </c>
       <c r="N164" t="n">
-        <v>12.49863818307099</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="O164" t="n">
-        <v>10.58917085120855</v>
+        <v>11.67311640680813</v>
       </c>
       <c r="P164" t="b">
         <v>1</v>
       </c>
       <c r="Q164" t="n">
-        <v>-5.075074155752257</v>
+        <v>4.581981658690704</v>
       </c>
     </row>
     <row r="165">
@@ -9996,25 +9852,25 @@
         <v>6</v>
       </c>
       <c r="K165" t="n">
-        <v>11.14795892046014</v>
+        <v>11.15692066664699</v>
       </c>
       <c r="L165" t="n">
         <v>25.13166948781075</v>
       </c>
       <c r="M165" t="n">
-        <v>8.671066277014619</v>
+        <v>10.62865290898554</v>
       </c>
       <c r="N165" t="n">
-        <v>12.5148122688107</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="O165" t="n">
-        <v>10.59293927291266</v>
+        <v>11.67311640680813</v>
       </c>
       <c r="P165" t="b">
         <v>1</v>
       </c>
       <c r="Q165" t="n">
-        <v>-5.239524491249825</v>
+        <v>4.422090229992715</v>
       </c>
     </row>
     <row r="166">
@@ -10055,25 +9911,25 @@
         <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="L166" t="n">
         <v>25.63145459768042</v>
       </c>
       <c r="M166" t="n">
-        <v>8.671060242963611</v>
+        <v>10.96189869435236</v>
       </c>
       <c r="N166" t="n">
-        <v>12.75516335641252</v>
+        <v>12.60397629558391</v>
       </c>
       <c r="O166" t="n">
-        <v>10.71311179968806</v>
+        <v>11.78293749496814</v>
       </c>
       <c r="P166" t="b">
         <v>1</v>
       </c>
       <c r="Q166" t="n">
-        <v>-12.55694170438175</v>
+        <v>-2.541445678945742</v>
       </c>
     </row>
     <row r="167">
@@ -10114,25 +9970,25 @@
         <v>6</v>
       </c>
       <c r="K167" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="L167" t="n">
         <v>25.64024316014946</v>
       </c>
       <c r="M167" t="n">
-        <v>8.671060242963611</v>
+        <v>10.96189869435236</v>
       </c>
       <c r="N167" t="n">
-        <v>12.75516335641252</v>
+        <v>12.60397629558391</v>
       </c>
       <c r="O167" t="n">
-        <v>10.71311179968806</v>
+        <v>11.78293749496814</v>
       </c>
       <c r="P167" t="b">
         <v>1</v>
       </c>
       <c r="Q167" t="n">
-        <v>-12.55694170438175</v>
+        <v>-2.541445678945742</v>
       </c>
     </row>
     <row r="168">
@@ -10173,25 +10029,25 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>12.05835100310014</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="L168" t="n">
         <v>25.64042578815858</v>
       </c>
       <c r="M168" t="n">
-        <v>8.671060242963611</v>
+        <v>10.96189869435236</v>
       </c>
       <c r="N168" t="n">
-        <v>12.75516335641252</v>
+        <v>12.60397629558391</v>
       </c>
       <c r="O168" t="n">
-        <v>10.71311179968806</v>
+        <v>11.78293749496814</v>
       </c>
       <c r="P168" t="b">
         <v>1</v>
       </c>
       <c r="Q168" t="n">
-        <v>-12.55694170438175</v>
+        <v>-2.541445678945742</v>
       </c>
     </row>
     <row r="169">
@@ -10232,25 +10088,25 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>12.7514670715484</v>
+        <v>12.77050304400545</v>
       </c>
       <c r="L169" t="n">
         <v>25.89474731761241</v>
       </c>
       <c r="M169" t="n">
-        <v>8.736947290759135</v>
+        <v>11.01112865213726</v>
       </c>
       <c r="N169" t="n">
-        <v>12.87172396313655</v>
+        <v>12.58638839885045</v>
       </c>
       <c r="O169" t="n">
-        <v>10.80433562694784</v>
+        <v>11.79875852549386</v>
       </c>
       <c r="P169" t="b">
         <v>1</v>
       </c>
       <c r="Q169" t="n">
-        <v>-18.02176007698317</v>
+        <v>-8.235989544255196</v>
       </c>
     </row>
     <row r="170">
@@ -10291,25 +10147,25 @@
         <v>6</v>
       </c>
       <c r="K170" t="n">
-        <v>12.99740495364647</v>
+        <v>13.02315010602378</v>
       </c>
       <c r="L170" t="n">
         <v>26.02142330428038</v>
       </c>
       <c r="M170" t="n">
-        <v>8.899453321332752</v>
+        <v>11.018354095561</v>
       </c>
       <c r="N170" t="n">
-        <v>12.91232242971177</v>
+        <v>12.57450141296879</v>
       </c>
       <c r="O170" t="n">
-        <v>10.90588787552226</v>
+        <v>11.79642775426489</v>
       </c>
       <c r="P170" t="b">
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>-19.1778707244783</v>
+        <v>-10.39910028114552</v>
       </c>
     </row>
     <row r="171">
@@ -10350,25 +10206,25 @@
         <v>6</v>
       </c>
       <c r="K171" t="n">
-        <v>13.22893290283062</v>
+        <v>13.21812533502401</v>
       </c>
       <c r="L171" t="n">
         <v>26.09848095840235</v>
       </c>
       <c r="M171" t="n">
-        <v>8.976878747685555</v>
+        <v>11.00953264575653</v>
       </c>
       <c r="N171" t="n">
-        <v>12.91033089851393</v>
+        <v>12.57450141296879</v>
       </c>
       <c r="O171" t="n">
-        <v>10.94360482309974</v>
+        <v>11.79201702936266</v>
       </c>
       <c r="P171" t="b">
         <v>1</v>
       </c>
       <c r="Q171" t="n">
-        <v>-20.88277232842886</v>
+        <v>-12.09384537106994</v>
       </c>
     </row>
     <row r="172">
@@ -10409,25 +10265,25 @@
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>13.38196974327161</v>
+        <v>13.40533484643394</v>
       </c>
       <c r="L172" t="n">
         <v>26.17727301948736</v>
       </c>
       <c r="M172" t="n">
-        <v>9.070594825751041</v>
+        <v>11.00953264575653</v>
       </c>
       <c r="N172" t="n">
-        <v>12.91033089851393</v>
+        <v>12.48355666974042</v>
       </c>
       <c r="O172" t="n">
-        <v>10.99046286213249</v>
+        <v>11.74654465774847</v>
       </c>
       <c r="P172" t="b">
         <v>1</v>
       </c>
       <c r="Q172" t="n">
-        <v>-21.75983769872902</v>
+        <v>-14.12151604592309</v>
       </c>
     </row>
     <row r="173">
@@ -10468,25 +10324,25 @@
         <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>13.52525134411477</v>
+        <v>13.537726437254</v>
       </c>
       <c r="L173" t="n">
         <v>26.26588402639144</v>
       </c>
       <c r="M173" t="n">
-        <v>9.070594825751041</v>
+        <v>10.89968555114491</v>
       </c>
       <c r="N173" t="n">
-        <v>12.80490227021584</v>
+        <v>12.48355666974042</v>
       </c>
       <c r="O173" t="n">
-        <v>10.93774854798344</v>
+        <v>11.69162111044266</v>
       </c>
       <c r="P173" t="b">
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>-23.65663083933651</v>
+        <v>-15.78998591702938</v>
       </c>
     </row>
     <row r="174">
@@ -10527,25 +10383,25 @@
         <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>13.52741702524259</v>
+        <v>13.537726437254</v>
       </c>
       <c r="L174" t="n">
         <v>26.2855363515403</v>
       </c>
       <c r="M174" t="n">
-        <v>9.070594825751041</v>
+        <v>10.89968555114491</v>
       </c>
       <c r="N174" t="n">
-        <v>12.80490227021584</v>
+        <v>12.48355666974042</v>
       </c>
       <c r="O174" t="n">
-        <v>10.93774854798344</v>
+        <v>11.69162111044266</v>
       </c>
       <c r="P174" t="b">
         <v>1</v>
       </c>
       <c r="Q174" t="n">
-        <v>-23.67643090256086</v>
+        <v>-15.78998591702938</v>
       </c>
     </row>
     <row r="175">
@@ -10586,25 +10442,25 @@
         <v>6</v>
       </c>
       <c r="K175" t="n">
-        <v>13.52513424291054</v>
+        <v>13.51603029642644</v>
       </c>
       <c r="L175" t="n">
         <v>26.61383911335768</v>
       </c>
       <c r="M175" t="n">
-        <v>9.549278556066488</v>
+        <v>10.53428444199073</v>
       </c>
       <c r="N175" t="n">
-        <v>12.7379435150013</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="O175" t="n">
-        <v>11.14361103553389</v>
+        <v>11.51048299048102</v>
       </c>
       <c r="P175" t="b">
         <v>1</v>
       </c>
       <c r="Q175" t="n">
-        <v>-21.37119825685434</v>
+        <v>-17.42365900374445</v>
       </c>
     </row>
     <row r="176">
@@ -10645,25 +10501,25 @@
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>13.45373608070102</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="L176" t="n">
         <v>26.67370607969477</v>
       </c>
       <c r="M176" t="n">
-        <v>9.549278556066488</v>
+        <v>10.53428444199073</v>
       </c>
       <c r="N176" t="n">
-        <v>12.6701704866137</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="O176" t="n">
-        <v>11.10972452134009</v>
+        <v>11.51048299048102</v>
       </c>
       <c r="P176" t="b">
         <v>1</v>
       </c>
       <c r="Q176" t="n">
-        <v>-21.09873701061116</v>
+        <v>-16.7488701260164</v>
       </c>
     </row>
     <row r="177">
@@ -10704,25 +10560,25 @@
         <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>13.45373608070102</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="L177" t="n">
         <v>26.67394357332298</v>
       </c>
       <c r="M177" t="n">
-        <v>9.549278556066488</v>
+        <v>10.53428444199073</v>
       </c>
       <c r="N177" t="n">
-        <v>12.6701704866137</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="O177" t="n">
-        <v>11.10972452134009</v>
+        <v>11.51048299048102</v>
       </c>
       <c r="P177" t="b">
         <v>1</v>
       </c>
       <c r="Q177" t="n">
-        <v>-21.09873701061116</v>
+        <v>-16.7488701260164</v>
       </c>
     </row>
     <row r="178">
@@ -10763,25 +10619,25 @@
         <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>12.87687986559452</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="L178" t="n">
         <v>27.10849213534284</v>
       </c>
       <c r="M178" t="n">
-        <v>9.954755082868157</v>
+        <v>9.515191599918353</v>
       </c>
       <c r="N178" t="n">
-        <v>12.28779173644725</v>
+        <v>12.44763178568168</v>
       </c>
       <c r="O178" t="n">
-        <v>11.1212734096577</v>
+        <v>10.98141169280002</v>
       </c>
       <c r="P178" t="b">
         <v>1</v>
       </c>
       <c r="Q178" t="n">
-        <v>-15.78602010100976</v>
+        <v>-17.20259046012487</v>
       </c>
     </row>
     <row r="179">
@@ -10822,25 +10678,25 @@
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>12.78203660848068</v>
+        <v>12.7867235364597</v>
       </c>
       <c r="L179" t="n">
         <v>27.35083465070139</v>
       </c>
       <c r="M179" t="n">
-        <v>10.238901419118</v>
+        <v>8.778468627187005</v>
       </c>
       <c r="N179" t="n">
-        <v>12.28779173644725</v>
+        <v>12.40318891736148</v>
       </c>
       <c r="O179" t="n">
-        <v>11.26334657778263</v>
+        <v>10.59082877227424</v>
       </c>
       <c r="P179" t="b">
         <v>1</v>
       </c>
       <c r="Q179" t="n">
-        <v>-13.48347065599254</v>
+        <v>-20.73392754620011</v>
       </c>
     </row>
     <row r="180">
@@ -10881,25 +10737,25 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>12.88732088272113</v>
+        <v>12.89096747702697</v>
       </c>
       <c r="L180" t="n">
         <v>27.59639603317916</v>
       </c>
       <c r="M180" t="n">
-        <v>10.26949459641317</v>
+        <v>8.766071098486607</v>
       </c>
       <c r="N180" t="n">
-        <v>11.88832606873517</v>
+        <v>12.18857742981998</v>
       </c>
       <c r="O180" t="n">
-        <v>11.07891033257417</v>
+        <v>10.47732426415329</v>
       </c>
       <c r="P180" t="b">
         <v>1</v>
       </c>
       <c r="Q180" t="n">
-        <v>-16.32300014948111</v>
+        <v>-23.03682841173125</v>
       </c>
     </row>
     <row r="181">
@@ -10940,25 +10796,25 @@
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>13.10364382962162</v>
+        <v>13.05682586052934</v>
       </c>
       <c r="L181" t="n">
         <v>27.86005273560105</v>
       </c>
       <c r="M181" t="n">
-        <v>10.19922334404454</v>
+        <v>8.660472291933454</v>
       </c>
       <c r="N181" t="n">
-        <v>11.88790187061831</v>
+        <v>12.08974146158847</v>
       </c>
       <c r="O181" t="n">
-        <v>11.04356260733143</v>
+        <v>10.37510687676096</v>
       </c>
       <c r="P181" t="b">
         <v>1</v>
       </c>
       <c r="Q181" t="n">
-        <v>-18.65413631034765</v>
+        <v>-25.84762755336161</v>
       </c>
     </row>
     <row r="182">
@@ -10999,25 +10855,25 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>13.21665282962994</v>
+        <v>13.28858676062679</v>
       </c>
       <c r="L182" t="n">
         <v>28.1331987669192</v>
       </c>
       <c r="M182" t="n">
-        <v>10.14784199584086</v>
+        <v>8.87437875450698</v>
       </c>
       <c r="N182" t="n">
-        <v>12.16318878177189</v>
+        <v>12.09182940507767</v>
       </c>
       <c r="O182" t="n">
-        <v>11.15551538880637</v>
+        <v>10.48310407979232</v>
       </c>
       <c r="P182" t="b">
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>-18.47639816706042</v>
+        <v>-26.76194626591975</v>
       </c>
     </row>
     <row r="183">
@@ -11058,25 +10914,25 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>13.22868636362987</v>
+        <v>13.22856214979317</v>
       </c>
       <c r="L183" t="n">
         <v>28.38741404583604</v>
       </c>
       <c r="M183" t="n">
-        <v>10.26983464027998</v>
+        <v>8.973642303512785</v>
       </c>
       <c r="N183" t="n">
-        <v>12.2850933308724</v>
+        <v>12.09598596468677</v>
       </c>
       <c r="O183" t="n">
-        <v>11.27746398557619</v>
+        <v>10.53481413409978</v>
       </c>
       <c r="P183" t="b">
         <v>1</v>
       </c>
       <c r="Q183" t="n">
-        <v>-17.30196062296698</v>
+        <v>-25.56996242557421</v>
       </c>
     </row>
     <row r="184">
@@ -11117,25 +10973,25 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>13.22836695411769</v>
+        <v>13.22815891986998</v>
       </c>
       <c r="L184" t="n">
         <v>28.41707791668021</v>
       </c>
       <c r="M184" t="n">
-        <v>10.26983464027998</v>
+        <v>9.158641167072478</v>
       </c>
       <c r="N184" t="n">
-        <v>12.2850933308724</v>
+        <v>12.10642473098731</v>
       </c>
       <c r="O184" t="n">
-        <v>11.27746398557619</v>
+        <v>10.63253294902989</v>
       </c>
       <c r="P184" t="b">
         <v>1</v>
       </c>
       <c r="Q184" t="n">
-        <v>-17.29912834159077</v>
+        <v>-24.41211311813434</v>
       </c>
     </row>
     <row r="185">
@@ -11176,25 +11032,25 @@
         <v>6</v>
       </c>
       <c r="K185" t="n">
-        <v>12.56331902858596</v>
+        <v>12.55278671512658</v>
       </c>
       <c r="L185" t="n">
         <v>28.80552420230507</v>
       </c>
       <c r="M185" t="n">
-        <v>10.54442709905314</v>
+        <v>9.151724631834414</v>
       </c>
       <c r="N185" t="n">
-        <v>12.46602379984828</v>
+        <v>12.2311785122366</v>
       </c>
       <c r="O185" t="n">
-        <v>11.50522544945071</v>
+        <v>10.69145157203551</v>
       </c>
       <c r="P185" t="b">
         <v>1</v>
       </c>
       <c r="Q185" t="n">
-        <v>-9.196634901107181</v>
+        <v>-17.40956436597969</v>
       </c>
     </row>
     <row r="186">
@@ -11235,25 +11091,25 @@
         <v>6</v>
       </c>
       <c r="K186" t="n">
-        <v>12.54081239321359</v>
+        <v>12.53041601577564</v>
       </c>
       <c r="L186" t="n">
         <v>28.83415833233666</v>
       </c>
       <c r="M186" t="n">
-        <v>10.54442709905314</v>
+        <v>9.151724631834414</v>
       </c>
       <c r="N186" t="n">
-        <v>12.46602379984828</v>
+        <v>12.2311785122366</v>
       </c>
       <c r="O186" t="n">
-        <v>11.50522544945071</v>
+        <v>10.69145157203551</v>
       </c>
       <c r="P186" t="b">
         <v>1</v>
       </c>
       <c r="Q186" t="n">
-        <v>-9.001013915918721</v>
+        <v>-17.20032524442345</v>
       </c>
     </row>
     <row r="187">
@@ -11294,25 +11150,25 @@
         <v>6</v>
       </c>
       <c r="K187" t="n">
-        <v>12.29943552785324</v>
+        <v>12.29751099175077</v>
       </c>
       <c r="L187" t="n">
         <v>29.07728195379162</v>
       </c>
       <c r="M187" t="n">
-        <v>10.75670064819602</v>
+        <v>9.205402671033942</v>
       </c>
       <c r="N187" t="n">
-        <v>12.52439545881572</v>
+        <v>12.39841015681416</v>
       </c>
       <c r="O187" t="n">
-        <v>11.64054805350587</v>
+        <v>10.80190641392405</v>
       </c>
       <c r="P187" t="b">
         <v>1</v>
       </c>
       <c r="Q187" t="n">
-        <v>-5.660278805764007</v>
+        <v>-13.84574648692416</v>
       </c>
     </row>
     <row r="188">
@@ -11353,25 +11209,25 @@
         <v>6</v>
       </c>
       <c r="K188" t="n">
-        <v>12.2829233494113</v>
+        <v>12.29277387507475</v>
       </c>
       <c r="L188" t="n">
         <v>29.15563283135659</v>
       </c>
       <c r="M188" t="n">
-        <v>10.83306256459373</v>
+        <v>9.205402671033942</v>
       </c>
       <c r="N188" t="n">
-        <v>12.52439545881572</v>
+        <v>12.63438262869062</v>
       </c>
       <c r="O188" t="n">
-        <v>11.67872901170472</v>
+        <v>10.91989264986228</v>
       </c>
       <c r="P188" t="b">
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>-5.173459689843263</v>
+        <v>-12.572295985252</v>
       </c>
     </row>
     <row r="189">
@@ -11412,25 +11268,25 @@
         <v>6</v>
       </c>
       <c r="K189" t="n">
-        <v>12.29630371710577</v>
+        <v>12.29958707864683</v>
       </c>
       <c r="L189" t="n">
         <v>29.31899634328527</v>
       </c>
       <c r="M189" t="n">
-        <v>10.92685448189717</v>
+        <v>9.403399618816287</v>
       </c>
       <c r="N189" t="n">
-        <v>12.54340224967523</v>
+        <v>12.6423103050087</v>
       </c>
       <c r="O189" t="n">
-        <v>11.7351283657862</v>
+        <v>11.0228549619125</v>
       </c>
       <c r="P189" t="b">
         <v>1</v>
       </c>
       <c r="Q189" t="n">
-        <v>-4.78201289178628</v>
+        <v>-11.58259018326788</v>
       </c>
     </row>
     <row r="190">
@@ -11471,25 +11327,25 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>12.30719348999601</v>
+        <v>12.3111585689887</v>
       </c>
       <c r="L190" t="n">
         <v>29.37188843089523</v>
       </c>
       <c r="M190" t="n">
-        <v>10.92685448189717</v>
+        <v>9.403399618816287</v>
       </c>
       <c r="N190" t="n">
-        <v>12.54340224967523</v>
+        <v>12.93319383577244</v>
       </c>
       <c r="O190" t="n">
-        <v>11.7351283657862</v>
+        <v>11.16829672729436</v>
       </c>
       <c r="P190" t="b">
         <v>1</v>
       </c>
       <c r="Q190" t="n">
-        <v>-4.874809259672586</v>
+        <v>-10.23308987574869</v>
       </c>
     </row>
     <row r="191">
@@ -11530,25 +11386,25 @@
         <v>6</v>
       </c>
       <c r="K191" t="n">
-        <v>12.35258897367873</v>
+        <v>12.35319462240552</v>
       </c>
       <c r="L191" t="n">
         <v>29.68906454090381</v>
       </c>
       <c r="M191" t="n">
-        <v>10.9708481273363</v>
+        <v>9.126831340801603</v>
       </c>
       <c r="N191" t="n">
-        <v>12.55626785778556</v>
+        <v>12.99985311520591</v>
       </c>
       <c r="O191" t="n">
-        <v>11.76355799256093</v>
+        <v>11.06334222800376</v>
       </c>
       <c r="P191" t="b">
         <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>-5.007251900235432</v>
+        <v>-11.65879503516458</v>
       </c>
     </row>
     <row r="192">
@@ -11589,25 +11445,25 @@
         <v>6</v>
       </c>
       <c r="K192" t="n">
-        <v>12.35296321494364</v>
+        <v>12.35342338176835</v>
       </c>
       <c r="L192" t="n">
         <v>29.70776010872902</v>
       </c>
       <c r="M192" t="n">
-        <v>10.95402348740476</v>
+        <v>9.126831340801603</v>
       </c>
       <c r="N192" t="n">
-        <v>12.55626785778556</v>
+        <v>12.99985311520591</v>
       </c>
       <c r="O192" t="n">
-        <v>11.75514567259516</v>
+        <v>11.06334222800376</v>
       </c>
       <c r="P192" t="b">
         <v>1</v>
       </c>
       <c r="Q192" t="n">
-        <v>-5.085581744360512</v>
+        <v>-11.66086275898719</v>
       </c>
     </row>
     <row r="193">
@@ -11648,25 +11504,25 @@
         <v>6</v>
       </c>
       <c r="K193" t="n">
-        <v>12.35296321494364</v>
+        <v>12.35342338176835</v>
       </c>
       <c r="L193" t="n">
         <v>29.70783208429308</v>
       </c>
       <c r="M193" t="n">
-        <v>10.95402348740476</v>
+        <v>9.126831340801603</v>
       </c>
       <c r="N193" t="n">
-        <v>12.55626785778556</v>
+        <v>12.99985311520591</v>
       </c>
       <c r="O193" t="n">
-        <v>11.75514567259516</v>
+        <v>11.06334222800376</v>
       </c>
       <c r="P193" t="b">
         <v>1</v>
       </c>
       <c r="Q193" t="n">
-        <v>-5.085581744360512</v>
+        <v>-11.66086275898719</v>
       </c>
     </row>
     <row r="194">
@@ -11707,25 +11563,25 @@
         <v>6</v>
       </c>
       <c r="K194" t="n">
-        <v>12.49863818307099</v>
+        <v>12.50552073045885</v>
       </c>
       <c r="L194" t="n">
         <v>30.09620259346922</v>
       </c>
       <c r="M194" t="n">
-        <v>11.14795892046014</v>
+        <v>8.670969426295731</v>
       </c>
       <c r="N194" t="n">
-        <v>12.71987453457647</v>
+        <v>11.20503957697606</v>
       </c>
       <c r="O194" t="n">
-        <v>11.9339167275183</v>
+        <v>9.938004501635897</v>
       </c>
       <c r="P194" t="b">
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>-4.73207135969449</v>
+        <v>-25.83532970225877</v>
       </c>
     </row>
     <row r="195">
@@ -11766,25 +11622,25 @@
         <v>6</v>
       </c>
       <c r="K195" t="n">
-        <v>12.5148122688107</v>
+        <v>12.52090093383555</v>
       </c>
       <c r="L195" t="n">
         <v>30.14356289869485</v>
       </c>
       <c r="M195" t="n">
-        <v>11.14795892046014</v>
+        <v>8.670969426295731</v>
       </c>
       <c r="N195" t="n">
-        <v>12.71987453457647</v>
+        <v>11.20503957697606</v>
       </c>
       <c r="O195" t="n">
-        <v>11.9339167275183</v>
+        <v>9.938004501635897</v>
       </c>
       <c r="P195" t="b">
         <v>1</v>
       </c>
       <c r="Q195" t="n">
-        <v>-4.867601765252116</v>
+        <v>-25.99009118756666</v>
       </c>
     </row>
     <row r="196">
@@ -11825,25 +11681,25 @@
         <v>6</v>
       </c>
       <c r="K196" t="n">
-        <v>12.64059519103216</v>
+        <v>12.64447152506395</v>
       </c>
       <c r="L196" t="n">
         <v>30.3335205295862</v>
       </c>
       <c r="M196" t="n">
-        <v>11.14795892046014</v>
+        <v>8.533079617107587</v>
       </c>
       <c r="N196" t="n">
-        <v>12.71883627017913</v>
+        <v>10.90493944776398</v>
       </c>
       <c r="O196" t="n">
-        <v>11.93339759531964</v>
+        <v>9.719009532435782</v>
       </c>
       <c r="P196" t="b">
         <v>1</v>
       </c>
       <c r="Q196" t="n">
-        <v>-5.926204922476486</v>
+        <v>-30.10041283388876</v>
       </c>
     </row>
     <row r="197">
@@ -11884,25 +11740,25 @@
         <v>6</v>
       </c>
       <c r="K197" t="n">
-        <v>12.75516335641252</v>
+        <v>12.74559832073476</v>
       </c>
       <c r="L197" t="n">
         <v>30.6607311421668</v>
       </c>
       <c r="M197" t="n">
-        <v>12.05835100310014</v>
+        <v>8.670332350741491</v>
       </c>
       <c r="N197" t="n">
-        <v>12.6066166473486</v>
+        <v>11.11747203295466</v>
       </c>
       <c r="O197" t="n">
-        <v>12.33248382522437</v>
+        <v>9.893902191848078</v>
       </c>
       <c r="P197" t="b">
         <v>1</v>
       </c>
       <c r="Q197" t="n">
-        <v>-3.427367407720583</v>
+        <v>-28.82276450272865</v>
       </c>
     </row>
     <row r="198">
@@ -11943,25 +11799,25 @@
         <v>6</v>
       </c>
       <c r="K198" t="n">
-        <v>12.82434787857481</v>
+        <v>12.82934323440308</v>
       </c>
       <c r="L198" t="n">
         <v>30.83130387152616</v>
       </c>
       <c r="M198" t="n">
-        <v>12.7514670715484</v>
+        <v>8.737214268524154</v>
       </c>
       <c r="N198" t="n">
-        <v>12.54480457182633</v>
+        <v>11.12288100999922</v>
       </c>
       <c r="O198" t="n">
-        <v>12.64813582168737</v>
+        <v>9.930047639261687</v>
       </c>
       <c r="P198" t="b">
         <v>1</v>
       </c>
       <c r="Q198" t="n">
-        <v>-1.393185994929791</v>
+        <v>-29.19719723879348</v>
       </c>
     </row>
     <row r="199">
@@ -12002,25 +11858,25 @@
         <v>6</v>
       </c>
       <c r="K199" t="n">
-        <v>12.87172396313655</v>
+        <v>12.87675709584725</v>
       </c>
       <c r="L199" t="n">
         <v>30.88335612175826</v>
       </c>
       <c r="M199" t="n">
-        <v>12.7514670715484</v>
+        <v>8.737214268524154</v>
       </c>
       <c r="N199" t="n">
-        <v>12.5861789188918</v>
+        <v>11.12288100999922</v>
       </c>
       <c r="O199" t="n">
-        <v>12.6688229952201</v>
+        <v>9.930047639261687</v>
       </c>
       <c r="P199" t="b">
         <v>1</v>
       </c>
       <c r="Q199" t="n">
-        <v>-1.60157709988531</v>
+        <v>-29.67467592939621</v>
       </c>
     </row>
     <row r="200">
@@ -12061,25 +11917,25 @@
         <v>6</v>
       </c>
       <c r="K200" t="n">
-        <v>12.91232242971177</v>
+        <v>12.91446486725206</v>
       </c>
       <c r="L200" t="n">
         <v>30.99288122060772</v>
       </c>
       <c r="M200" t="n">
-        <v>12.99740495364647</v>
+        <v>8.908018607468405</v>
       </c>
       <c r="N200" t="n">
-        <v>12.54329025449246</v>
+        <v>11.32387376443929</v>
       </c>
       <c r="O200" t="n">
-        <v>12.77034760406947</v>
+        <v>10.11594618595385</v>
       </c>
       <c r="P200" t="b">
         <v>1</v>
       </c>
       <c r="Q200" t="n">
-        <v>-1.111753806897653</v>
+        <v>-27.66442831797582</v>
       </c>
     </row>
     <row r="201">
@@ -12120,25 +11976,25 @@
         <v>6</v>
       </c>
       <c r="K201" t="n">
-        <v>12.91033089851393</v>
+        <v>12.90839304015632</v>
       </c>
       <c r="L201" t="n">
         <v>31.11267869945013</v>
       </c>
       <c r="M201" t="n">
-        <v>13.22893290283062</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="N201" t="n">
-        <v>12.54329025449246</v>
+        <v>11.42106618993412</v>
       </c>
       <c r="O201" t="n">
-        <v>12.88611157866154</v>
+        <v>10.25166170880558</v>
       </c>
       <c r="P201" t="b">
         <v>1</v>
       </c>
       <c r="Q201" t="n">
-        <v>-0.1879490155315633</v>
+        <v>-25.91512875487068</v>
       </c>
     </row>
     <row r="202">
@@ -12179,25 +12035,25 @@
         <v>6</v>
       </c>
       <c r="K202" t="n">
-        <v>12.80490227021584</v>
+        <v>12.80505334864713</v>
       </c>
       <c r="L202" t="n">
         <v>31.38616691414873</v>
       </c>
       <c r="M202" t="n">
-        <v>13.52741702524259</v>
+        <v>9.082257227677049</v>
       </c>
       <c r="N202" t="n">
-        <v>12.47721645407332</v>
+        <v>11.60571276836865</v>
       </c>
       <c r="O202" t="n">
-        <v>13.00231673965795</v>
+        <v>10.34398499802285</v>
       </c>
       <c r="P202" t="b">
         <v>1</v>
       </c>
       <c r="Q202" t="n">
-        <v>1.518302264087967</v>
+        <v>-23.79226527392195</v>
       </c>
     </row>
     <row r="203">
@@ -12238,25 +12094,25 @@
         <v>6</v>
       </c>
       <c r="K203" t="n">
-        <v>12.802726964012</v>
+        <v>12.80470013952624</v>
       </c>
       <c r="L203" t="n">
         <v>31.40989843741151</v>
       </c>
       <c r="M203" t="n">
-        <v>13.52741702524259</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="N203" t="n">
-        <v>12.49451825327216</v>
+        <v>11.63462537719781</v>
       </c>
       <c r="O203" t="n">
-        <v>13.01096763925738</v>
+        <v>10.56391642543833</v>
       </c>
       <c r="P203" t="b">
         <v>1</v>
       </c>
       <c r="Q203" t="n">
-        <v>1.600501062019843</v>
+        <v>-21.21167589599649</v>
       </c>
     </row>
     <row r="204">
@@ -12297,25 +12153,25 @@
         <v>6</v>
       </c>
       <c r="K204" t="n">
-        <v>12.7379435150013</v>
+        <v>12.73965880607229</v>
       </c>
       <c r="L204" t="n">
         <v>31.57992202709708</v>
       </c>
       <c r="M204" t="n">
-        <v>13.52513424291054</v>
+        <v>9.493207473678842</v>
       </c>
       <c r="N204" t="n">
-        <v>12.50066545811739</v>
+        <v>11.59495023728868</v>
       </c>
       <c r="O204" t="n">
-        <v>13.01289985051397</v>
+        <v>10.54407885548376</v>
       </c>
       <c r="P204" t="b">
         <v>1</v>
       </c>
       <c r="Q204" t="n">
-        <v>2.112952060426487</v>
+        <v>-20.82287111734429</v>
       </c>
     </row>
     <row r="205">
@@ -12356,25 +12212,25 @@
         <v>6</v>
       </c>
       <c r="K205" t="n">
-        <v>12.6701704866137</v>
+        <v>12.66848637001136</v>
       </c>
       <c r="L205" t="n">
         <v>31.71136369563923</v>
       </c>
       <c r="M205" t="n">
-        <v>13.45373608070102</v>
+        <v>9.562461236943456</v>
       </c>
       <c r="N205" t="n">
-        <v>12.50066545811739</v>
+        <v>11.47413396052639</v>
       </c>
       <c r="O205" t="n">
-        <v>12.9772007694092</v>
+        <v>10.51829759873492</v>
       </c>
       <c r="P205" t="b">
         <v>1</v>
       </c>
       <c r="Q205" t="n">
-        <v>2.365920727058957</v>
+        <v>-20.44236485127644</v>
       </c>
     </row>
     <row r="206">
@@ -12415,25 +12271,25 @@
         <v>6</v>
       </c>
       <c r="K206" t="n">
-        <v>12.6701704866137</v>
+        <v>12.66848637001136</v>
       </c>
       <c r="L206" t="n">
         <v>31.71188940465948</v>
       </c>
       <c r="M206" t="n">
-        <v>13.45373608070102</v>
+        <v>9.562461236943456</v>
       </c>
       <c r="N206" t="n">
-        <v>12.50066545811739</v>
+        <v>11.47413396052639</v>
       </c>
       <c r="O206" t="n">
-        <v>12.9772007694092</v>
+        <v>10.51829759873492</v>
       </c>
       <c r="P206" t="b">
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>2.365920727058957</v>
+        <v>-20.44236485127644</v>
       </c>
     </row>
     <row r="207">
@@ -12474,25 +12330,25 @@
         <v>6</v>
       </c>
       <c r="K207" t="n">
-        <v>12.49945175787417</v>
+        <v>12.50157920325796</v>
       </c>
       <c r="L207" t="n">
         <v>31.91656463622267</v>
       </c>
       <c r="M207" t="n">
-        <v>12.87687986559452</v>
+        <v>9.977092619200015</v>
       </c>
       <c r="N207" t="n">
-        <v>12.55371901573918</v>
+        <v>11.32954314383762</v>
       </c>
       <c r="O207" t="n">
-        <v>12.71529944066685</v>
+        <v>10.65331788151882</v>
       </c>
       <c r="P207" t="b">
         <v>1</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.697543056692319</v>
+        <v>-17.34916147527594</v>
       </c>
     </row>
     <row r="208">
@@ -12533,25 +12389,25 @@
         <v>6</v>
       </c>
       <c r="K208" t="n">
-        <v>12.28779173644725</v>
+        <v>12.27482045438042</v>
       </c>
       <c r="L208" t="n">
         <v>32.13117026266667</v>
       </c>
       <c r="M208" t="n">
-        <v>12.87687986559452</v>
+        <v>10.08724170276781</v>
       </c>
       <c r="N208" t="n">
-        <v>12.45332192399493</v>
+        <v>11.13895581474152</v>
       </c>
       <c r="O208" t="n">
-        <v>12.66510089479473</v>
+        <v>10.61309875875466</v>
       </c>
       <c r="P208" t="b">
         <v>1</v>
       </c>
       <c r="Q208" t="n">
-        <v>2.979124773514852</v>
+        <v>-15.65727157918899</v>
       </c>
     </row>
     <row r="209">
@@ -12592,25 +12448,25 @@
         <v>6</v>
       </c>
       <c r="K209" t="n">
-        <v>11.88832606873517</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="L209" t="n">
         <v>32.6946598223415</v>
       </c>
       <c r="M209" t="n">
-        <v>12.88732088272113</v>
+        <v>10.26722045282886</v>
       </c>
       <c r="N209" t="n">
-        <v>12.19413671075773</v>
+        <v>10.99471119916965</v>
       </c>
       <c r="O209" t="n">
-        <v>12.54072879673943</v>
+        <v>10.63096582599925</v>
       </c>
       <c r="P209" t="b">
         <v>1</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.202271244187062</v>
+        <v>-11.8121124798046</v>
       </c>
     </row>
     <row r="210">
@@ -12651,25 +12507,25 @@
         <v>6</v>
       </c>
       <c r="K210" t="n">
-        <v>11.88790187061831</v>
+        <v>11.88670746705587</v>
       </c>
       <c r="L210" t="n">
         <v>32.70437492689629</v>
       </c>
       <c r="M210" t="n">
-        <v>12.88732088272113</v>
+        <v>10.26722045282886</v>
       </c>
       <c r="N210" t="n">
-        <v>12.19413671075773</v>
+        <v>10.99471119916965</v>
       </c>
       <c r="O210" t="n">
-        <v>12.54072879673943</v>
+        <v>10.63096582599925</v>
       </c>
       <c r="P210" t="b">
         <v>1</v>
       </c>
       <c r="Q210" t="n">
-        <v>5.205653807702526</v>
+        <v>-11.8121124798046</v>
       </c>
     </row>
     <row r="211">
@@ -12710,25 +12566,25 @@
         <v>6</v>
       </c>
       <c r="K211" t="n">
-        <v>12.16318878177189</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="L211" t="n">
         <v>33.1811909613405</v>
       </c>
       <c r="M211" t="n">
-        <v>13.21665282962994</v>
+        <v>10.14758974514527</v>
       </c>
       <c r="N211" t="n">
-        <v>12.09182775173085</v>
+        <v>10.87185681435206</v>
       </c>
       <c r="O211" t="n">
-        <v>12.65424029068039</v>
+        <v>10.50972327974867</v>
       </c>
       <c r="P211" t="b">
         <v>1</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.880529353233109</v>
+        <v>-15.79229375620146</v>
       </c>
     </row>
     <row r="212">
@@ -12769,25 +12625,25 @@
         <v>6</v>
       </c>
       <c r="K212" t="n">
-        <v>12.16318878177189</v>
+        <v>12.16944965305047</v>
       </c>
       <c r="L212" t="n">
         <v>33.19271597431592</v>
       </c>
       <c r="M212" t="n">
-        <v>13.21665282962994</v>
+        <v>10.14758974514527</v>
       </c>
       <c r="N212" t="n">
-        <v>12.09182775173085</v>
+        <v>10.87185681435206</v>
       </c>
       <c r="O212" t="n">
-        <v>12.65424029068039</v>
+        <v>10.50972327974867</v>
       </c>
       <c r="P212" t="b">
         <v>1</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.880529353233109</v>
+        <v>-15.79229375620146</v>
       </c>
     </row>
     <row r="213">
@@ -12828,25 +12684,25 @@
         <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>12.2850933308724</v>
+        <v>12.27993027022316</v>
       </c>
       <c r="L213" t="n">
         <v>33.42270019800137</v>
       </c>
       <c r="M213" t="n">
-        <v>13.22836695411769</v>
+        <v>10.27903163951837</v>
       </c>
       <c r="N213" t="n">
-        <v>12.1052150235773</v>
+        <v>10.77889366400938</v>
       </c>
       <c r="O213" t="n">
-        <v>12.6667909888475</v>
+        <v>10.52896265176387</v>
       </c>
       <c r="P213" t="b">
         <v>1</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.013372986979634</v>
+        <v>-16.63001072727668</v>
       </c>
     </row>
     <row r="214">
@@ -12887,25 +12743,25 @@
         <v>6</v>
       </c>
       <c r="K214" t="n">
-        <v>12.30729200089643</v>
+        <v>12.28702891766755</v>
       </c>
       <c r="L214" t="n">
         <v>33.46872642813639</v>
       </c>
       <c r="M214" t="n">
-        <v>13.22836695411769</v>
+        <v>10.27903163951837</v>
       </c>
       <c r="N214" t="n">
-        <v>12.1067013623614</v>
+        <v>10.77889366400938</v>
       </c>
       <c r="O214" t="n">
-        <v>12.66753415823955</v>
+        <v>10.52896265176387</v>
       </c>
       <c r="P214" t="b">
         <v>1</v>
       </c>
       <c r="Q214" t="n">
-        <v>2.843822269141449</v>
+        <v>-16.69743092506037</v>
       </c>
     </row>
     <row r="215">
@@ -12946,25 +12802,25 @@
         <v>6</v>
       </c>
       <c r="K215" t="n">
-        <v>12.46602379984828</v>
+        <v>12.46436863874414</v>
       </c>
       <c r="L215" t="n">
         <v>33.84894591262252</v>
       </c>
       <c r="M215" t="n">
-        <v>12.54081239321359</v>
+        <v>10.55296270291239</v>
       </c>
       <c r="N215" t="n">
-        <v>12.229154793299</v>
+        <v>10.37866941025346</v>
       </c>
       <c r="O215" t="n">
-        <v>12.3849835932563</v>
+        <v>10.46581605658292</v>
       </c>
       <c r="P215" t="b">
         <v>1</v>
       </c>
       <c r="Q215" t="n">
-        <v>-0.6543424622387661</v>
+        <v>-19.09600332507415</v>
       </c>
     </row>
     <row r="216">
@@ -13005,25 +12861,25 @@
         <v>6</v>
       </c>
       <c r="K216" t="n">
-        <v>12.49982119715622</v>
+        <v>12.49027804851815</v>
       </c>
       <c r="L216" t="n">
         <v>33.92795381720412</v>
       </c>
       <c r="M216" t="n">
-        <v>12.54081239321359</v>
+        <v>10.62689904180005</v>
       </c>
       <c r="N216" t="n">
-        <v>12.39318867506093</v>
+        <v>10.37866941025346</v>
       </c>
       <c r="O216" t="n">
-        <v>12.46700053413726</v>
+        <v>10.50278422602675</v>
       </c>
       <c r="P216" t="b">
         <v>1</v>
       </c>
       <c r="Q216" t="n">
-        <v>-0.2632603000945588</v>
+        <v>-18.9234947583349</v>
       </c>
     </row>
     <row r="217">
@@ -13064,25 +12920,25 @@
         <v>6</v>
       </c>
       <c r="K217" t="n">
-        <v>12.52439545881572</v>
+        <v>12.51606374896549</v>
       </c>
       <c r="L217" t="n">
         <v>34.21762017141074</v>
       </c>
       <c r="M217" t="n">
-        <v>12.2829233494113</v>
+        <v>10.84256885912033</v>
       </c>
       <c r="N217" t="n">
-        <v>12.63399979306722</v>
+        <v>9.863821606315435</v>
       </c>
       <c r="O217" t="n">
-        <v>12.45846157123926</v>
+        <v>10.35319523271788</v>
       </c>
       <c r="P217" t="b">
         <v>1</v>
       </c>
       <c r="Q217" t="n">
-        <v>-0.529229770461126</v>
+        <v>-20.89083097180062</v>
       </c>
     </row>
     <row r="218">
@@ -13123,25 +12979,25 @@
         <v>6</v>
       </c>
       <c r="K218" t="n">
-        <v>12.54340224967523</v>
+        <v>12.54276937654406</v>
       </c>
       <c r="L218" t="n">
         <v>34.36020504545638</v>
       </c>
       <c r="M218" t="n">
-        <v>12.30719348999601</v>
+        <v>10.9287005537623</v>
       </c>
       <c r="N218" t="n">
-        <v>12.92361940445302</v>
+        <v>9.863821606315435</v>
       </c>
       <c r="O218" t="n">
-        <v>12.61540644722452</v>
+        <v>10.39626108003887</v>
       </c>
       <c r="P218" t="b">
         <v>1</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.5707639928250408</v>
+        <v>-20.64692565894239</v>
       </c>
     </row>
     <row r="219">
@@ -13182,25 +13038,25 @@
         <v>6</v>
       </c>
       <c r="K219" t="n">
-        <v>12.57716517946826</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="L219" t="n">
         <v>34.49650626022285</v>
       </c>
       <c r="M219" t="n">
-        <v>12.30719348999601</v>
+        <v>10.94679446313857</v>
       </c>
       <c r="N219" t="n">
-        <v>12.92361940445302</v>
+        <v>9.705319379086149</v>
       </c>
       <c r="O219" t="n">
-        <v>12.61540644722452</v>
+        <v>10.32605692111236</v>
       </c>
       <c r="P219" t="b">
         <v>1</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.3031314759158299</v>
+        <v>-21.80354176456634</v>
       </c>
     </row>
     <row r="220">
@@ -13241,25 +13097,25 @@
         <v>6</v>
       </c>
       <c r="K220" t="n">
-        <v>12.57716517946826</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="L220" t="n">
         <v>34.49705174859361</v>
       </c>
       <c r="M220" t="n">
-        <v>12.30719348999601</v>
+        <v>10.94679446313857</v>
       </c>
       <c r="N220" t="n">
-        <v>12.92361940445302</v>
+        <v>9.705319379086149</v>
       </c>
       <c r="O220" t="n">
-        <v>12.61540644722452</v>
+        <v>10.32605692111236</v>
       </c>
       <c r="P220" t="b">
         <v>1</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.3031314759158299</v>
+        <v>-21.80354176456634</v>
       </c>
     </row>
     <row r="221">
@@ -13300,25 +13156,25 @@
         <v>6</v>
       </c>
       <c r="K221" t="n">
-        <v>12.55626785778556</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="L221" t="n">
         <v>34.8383717829181</v>
       </c>
       <c r="M221" t="n">
-        <v>12.35296321494364</v>
+        <v>10.95155561779406</v>
       </c>
       <c r="N221" t="n">
-        <v>13.00581980539971</v>
+        <v>9.555403531742021</v>
       </c>
       <c r="O221" t="n">
-        <v>12.67939151017168</v>
+        <v>10.25347957476804</v>
       </c>
       <c r="P221" t="b">
         <v>1</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.9710533213470818</v>
+        <v>-22.49273306306356</v>
       </c>
     </row>
     <row r="222">
@@ -13359,25 +13215,25 @@
         <v>6</v>
       </c>
       <c r="K222" t="n">
-        <v>12.71987453457647</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="L222" t="n">
         <v>35.2603864436309</v>
       </c>
       <c r="M222" t="n">
-        <v>12.64059519103216</v>
+        <v>11.15692066664699</v>
       </c>
       <c r="N222" t="n">
-        <v>10.91295735455809</v>
+        <v>10.12230649472664</v>
       </c>
       <c r="O222" t="n">
-        <v>11.77677627279513</v>
+        <v>10.63961358068682</v>
       </c>
       <c r="P222" t="b">
         <v>1</v>
       </c>
       <c r="Q222" t="n">
-        <v>-8.008119029652793</v>
+        <v>-19.53046798349776</v>
       </c>
     </row>
     <row r="223">
@@ -13418,25 +13274,25 @@
         <v>6</v>
       </c>
       <c r="K223" t="n">
-        <v>12.71883627017913</v>
+        <v>12.71667284304397</v>
       </c>
       <c r="L223" t="n">
         <v>35.30684831691412</v>
       </c>
       <c r="M223" t="n">
-        <v>12.64059519103216</v>
+        <v>11.15692066664699</v>
       </c>
       <c r="N223" t="n">
-        <v>10.91295735455809</v>
+        <v>10.12230649472664</v>
       </c>
       <c r="O223" t="n">
-        <v>11.77677627279513</v>
+        <v>10.63961358068682</v>
       </c>
       <c r="P223" t="b">
         <v>1</v>
       </c>
       <c r="Q223" t="n">
-        <v>-7.999302827550592</v>
+        <v>-19.52194265896516</v>
       </c>
     </row>
     <row r="224">
@@ -13477,25 +13333,25 @@
         <v>6</v>
       </c>
       <c r="K224" t="n">
-        <v>12.6066166473486</v>
+        <v>12.60397629558391</v>
       </c>
       <c r="L224" t="n">
         <v>35.59626007520095</v>
       </c>
       <c r="M224" t="n">
-        <v>12.75516335641252</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="N224" t="n">
-        <v>11.11067537123716</v>
+        <v>10.47758980818898</v>
       </c>
       <c r="O224" t="n">
-        <v>11.93291936382484</v>
+        <v>11.27999212948793</v>
       </c>
       <c r="P224" t="b">
         <v>1</v>
       </c>
       <c r="Q224" t="n">
-        <v>-5.645703812983949</v>
+        <v>-11.73745647069069</v>
       </c>
     </row>
     <row r="225">
@@ -13536,25 +13392,25 @@
         <v>6</v>
       </c>
       <c r="K225" t="n">
-        <v>12.56723055679825</v>
+        <v>12.56827758091871</v>
       </c>
       <c r="L225" t="n">
         <v>35.72675416193334</v>
       </c>
       <c r="M225" t="n">
-        <v>12.75516335641252</v>
+        <v>12.08239445078688</v>
       </c>
       <c r="N225" t="n">
-        <v>11.11067537123716</v>
+        <v>20.11034191780546</v>
       </c>
       <c r="O225" t="n">
-        <v>11.93291936382484</v>
+        <v>16.09636818429617</v>
       </c>
       <c r="P225" t="b">
         <v>1</v>
       </c>
       <c r="Q225" t="n">
-        <v>-5.315641324924658</v>
+        <v>21.91855058844583</v>
       </c>
     </row>
     <row r="226">
@@ -13595,25 +13451,25 @@
         <v>6</v>
       </c>
       <c r="K226" t="n">
-        <v>12.54480457182633</v>
+        <v>12.5514918954519</v>
       </c>
       <c r="L226" t="n">
         <v>35.79549466329404</v>
       </c>
       <c r="M226" t="n">
-        <v>12.82434787857481</v>
+        <v>12.77050304400545</v>
       </c>
       <c r="N226" t="n">
-        <v>11.11067537123716</v>
+        <v>24.57628309984061</v>
       </c>
       <c r="O226" t="n">
-        <v>11.96751162490598</v>
+        <v>18.67339307192303</v>
       </c>
       <c r="P226" t="b">
         <v>1</v>
       </c>
       <c r="Q226" t="n">
-        <v>-4.823834436215857</v>
+        <v>32.78408563934699</v>
       </c>
     </row>
     <row r="227">
@@ -13654,25 +13510,25 @@
         <v>6</v>
       </c>
       <c r="K227" t="n">
-        <v>12.5861789188918</v>
+        <v>12.58638839885045</v>
       </c>
       <c r="L227" t="n">
         <v>35.86896290621365</v>
       </c>
       <c r="M227" t="n">
-        <v>12.87172396313655</v>
+        <v>12.77050304400545</v>
       </c>
       <c r="N227" t="n">
-        <v>11.12092613981406</v>
+        <v>24.57628309984061</v>
       </c>
       <c r="O227" t="n">
-        <v>11.99632505147531</v>
+        <v>18.67339307192303</v>
       </c>
       <c r="P227" t="b">
         <v>1</v>
       </c>
       <c r="Q227" t="n">
-        <v>-4.916954691419906</v>
+        <v>32.59720742570823</v>
       </c>
     </row>
     <row r="228">
@@ -13713,25 +13569,25 @@
         <v>6</v>
       </c>
       <c r="K228" t="n">
-        <v>12.54329025449246</v>
+        <v>12.57450141296879</v>
       </c>
       <c r="L228" t="n">
         <v>35.97525808959312</v>
       </c>
       <c r="M228" t="n">
-        <v>12.91232242971177</v>
+        <v>13.02315010602378</v>
       </c>
       <c r="N228" t="n">
-        <v>11.41452067011062</v>
+        <v>27.18225840910968</v>
       </c>
       <c r="O228" t="n">
-        <v>12.1634215499112</v>
+        <v>20.10270425756673</v>
       </c>
       <c r="P228" t="b">
         <v>1</v>
       </c>
       <c r="Q228" t="n">
-        <v>-3.123041514449798</v>
+        <v>37.44870713980832</v>
       </c>
     </row>
     <row r="229">
@@ -13772,25 +13628,25 @@
         <v>6</v>
       </c>
       <c r="K229" t="n">
-        <v>12.54329025449246</v>
+        <v>12.57450141296879</v>
       </c>
       <c r="L229" t="n">
         <v>35.97567929850863</v>
       </c>
       <c r="M229" t="n">
-        <v>12.91232242971177</v>
+        <v>13.02315010602378</v>
       </c>
       <c r="N229" t="n">
-        <v>11.41452067011062</v>
+        <v>27.18225840910968</v>
       </c>
       <c r="O229" t="n">
-        <v>12.1634215499112</v>
+        <v>20.10270425756673</v>
       </c>
       <c r="P229" t="b">
         <v>1</v>
       </c>
       <c r="Q229" t="n">
-        <v>-3.123041514449798</v>
+        <v>37.44870713980832</v>
       </c>
     </row>
     <row r="230">
@@ -13831,25 +13687,25 @@
         <v>6</v>
       </c>
       <c r="K230" t="n">
-        <v>12.47729707886387</v>
+        <v>12.48355666974042</v>
       </c>
       <c r="L230" t="n">
         <v>36.29602454522568</v>
       </c>
       <c r="M230" t="n">
-        <v>12.80490227021584</v>
+        <v>13.537726437254</v>
       </c>
       <c r="N230" t="n">
-        <v>11.60063562855445</v>
+        <v>13.29960713304792</v>
       </c>
       <c r="O230" t="n">
-        <v>12.20276894938515</v>
+        <v>13.41866678515096</v>
       </c>
       <c r="P230" t="b">
         <v>1</v>
       </c>
       <c r="Q230" t="n">
-        <v>-2.249719966160257</v>
+        <v>6.96872595752458</v>
       </c>
     </row>
     <row r="231">
@@ -13890,25 +13746,25 @@
         <v>6</v>
       </c>
       <c r="K231" t="n">
-        <v>12.47721645407332</v>
+        <v>12.48340261345813</v>
       </c>
       <c r="L231" t="n">
         <v>36.32982528508303</v>
       </c>
       <c r="M231" t="n">
-        <v>12.80490227021584</v>
+        <v>13.537726437254</v>
       </c>
       <c r="N231" t="n">
-        <v>11.60063562855445</v>
+        <v>13.29960713304792</v>
       </c>
       <c r="O231" t="n">
-        <v>12.20276894938515</v>
+        <v>13.41866678515096</v>
       </c>
       <c r="P231" t="b">
         <v>1</v>
       </c>
       <c r="Q231" t="n">
-        <v>-2.249059257177843</v>
+        <v>6.969874031955136</v>
       </c>
     </row>
     <row r="232">
@@ -13949,25 +13805,25 @@
         <v>6</v>
       </c>
       <c r="K232" t="n">
-        <v>12.49451825327216</v>
+        <v>12.48171924833751</v>
       </c>
       <c r="L232" t="n">
         <v>36.48862583483739</v>
       </c>
       <c r="M232" t="n">
-        <v>12.802726964012</v>
+        <v>13.51603029642644</v>
       </c>
       <c r="N232" t="n">
-        <v>11.63492252765004</v>
+        <v>8.866998949237681</v>
       </c>
       <c r="O232" t="n">
-        <v>12.21882474583102</v>
+        <v>11.19151462283206</v>
       </c>
       <c r="P232" t="b">
         <v>1</v>
       </c>
       <c r="Q232" t="n">
-        <v>-2.25630134792798</v>
+        <v>-11.52841835075011</v>
       </c>
     </row>
     <row r="233">
@@ -14008,25 +13864,25 @@
         <v>6</v>
       </c>
       <c r="K233" t="n">
-        <v>12.49451825327216</v>
+        <v>12.48171924833751</v>
       </c>
       <c r="L233" t="n">
         <v>36.48990347940555</v>
       </c>
       <c r="M233" t="n">
-        <v>12.802726964012</v>
+        <v>13.51603029642644</v>
       </c>
       <c r="N233" t="n">
-        <v>11.63492252765004</v>
+        <v>8.866998949237681</v>
       </c>
       <c r="O233" t="n">
-        <v>12.21882474583102</v>
+        <v>11.19151462283206</v>
       </c>
       <c r="P233" t="b">
         <v>1</v>
       </c>
       <c r="Q233" t="n">
-        <v>-2.25630134792798</v>
+        <v>-11.52841835075011</v>
       </c>
     </row>
     <row r="234">
@@ -14067,25 +13923,25 @@
         <v>6</v>
       </c>
       <c r="K234" t="n">
-        <v>12.50066545811739</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="L234" t="n">
         <v>36.65810842832439</v>
       </c>
       <c r="M234" t="n">
-        <v>12.6701704866137</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="N234" t="n">
-        <v>11.47482411747132</v>
+        <v>8.866998949237681</v>
       </c>
       <c r="O234" t="n">
-        <v>12.07249730204251</v>
+        <v>11.15267889333579</v>
       </c>
       <c r="P234" t="b">
         <v>1</v>
       </c>
       <c r="Q234" t="n">
-        <v>-3.546641141120377</v>
+        <v>-11.96127547824091</v>
       </c>
     </row>
     <row r="235">
@@ -14126,25 +13982,25 @@
         <v>6</v>
       </c>
       <c r="K235" t="n">
-        <v>12.50066545811739</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="L235" t="n">
         <v>36.66438591343145</v>
       </c>
       <c r="M235" t="n">
-        <v>12.6701704866137</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="N235" t="n">
-        <v>11.47482411747132</v>
+        <v>8.866998949237681</v>
       </c>
       <c r="O235" t="n">
-        <v>12.07249730204251</v>
+        <v>11.15267889333579</v>
       </c>
       <c r="P235" t="b">
         <v>1</v>
       </c>
       <c r="Q235" t="n">
-        <v>-3.546641141120377</v>
+        <v>-11.96127547824091</v>
       </c>
     </row>
     <row r="236">
@@ -14185,25 +14041,25 @@
         <v>6</v>
       </c>
       <c r="K236" t="n">
-        <v>12.5438949370723</v>
+        <v>12.5439341252388</v>
       </c>
       <c r="L236" t="n">
         <v>36.83664322996535</v>
       </c>
       <c r="M236" t="n">
-        <v>12.49945175787417</v>
+        <v>13.43835883743389</v>
       </c>
       <c r="N236" t="n">
-        <v>11.41973742778242</v>
+        <v>7.896421559362166</v>
       </c>
       <c r="O236" t="n">
-        <v>11.9595945928283</v>
+        <v>10.66739019839803</v>
       </c>
       <c r="P236" t="b">
         <v>1</v>
       </c>
       <c r="Q236" t="n">
-        <v>-4.885619990784495</v>
+        <v>-17.59140606971123</v>
       </c>
     </row>
     <row r="237">
@@ -14244,25 +14100,25 @@
         <v>6</v>
       </c>
       <c r="K237" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54848340969551</v>
       </c>
       <c r="L237" t="n">
         <v>36.92689354462617</v>
       </c>
       <c r="M237" t="n">
-        <v>12.49945175787417</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N237" t="n">
-        <v>11.33187334346197</v>
+        <v>8.100198964353241</v>
       </c>
       <c r="O237" t="n">
-        <v>11.91566255066807</v>
+        <v>10.48534896870295</v>
       </c>
       <c r="P237" t="b">
         <v>1</v>
       </c>
       <c r="Q237" t="n">
-        <v>-5.354771187568863</v>
+        <v>-19.67635457008319</v>
       </c>
     </row>
     <row r="238">
@@ -14303,25 +14159,25 @@
         <v>6</v>
       </c>
       <c r="K238" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54830848625804</v>
       </c>
       <c r="L238" t="n">
         <v>36.92762739561841</v>
       </c>
       <c r="M238" t="n">
-        <v>12.49945175787417</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N238" t="n">
-        <v>11.33187334346197</v>
+        <v>8.100198964353241</v>
       </c>
       <c r="O238" t="n">
-        <v>11.91566255066807</v>
+        <v>10.48534896870295</v>
       </c>
       <c r="P238" t="b">
         <v>1</v>
       </c>
       <c r="Q238" t="n">
-        <v>-5.354771187568863</v>
+        <v>-19.6746863047923</v>
       </c>
     </row>
     <row r="239">
@@ -14362,25 +14218,25 @@
         <v>6</v>
       </c>
       <c r="K239" t="n">
-        <v>12.55371901573918</v>
+        <v>12.54830848625804</v>
       </c>
       <c r="L239" t="n">
         <v>36.95152828201871</v>
       </c>
       <c r="M239" t="n">
-        <v>12.49945175787417</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N239" t="n">
-        <v>11.33187334346197</v>
+        <v>8.100198964353241</v>
       </c>
       <c r="O239" t="n">
-        <v>11.91566255066807</v>
+        <v>10.48534896870295</v>
       </c>
       <c r="P239" t="b">
         <v>1</v>
       </c>
       <c r="Q239" t="n">
-        <v>-5.354771187568863</v>
+        <v>-19.6746863047923</v>
       </c>
     </row>
     <row r="240">
@@ -14421,25 +14277,25 @@
         <v>6</v>
       </c>
       <c r="K240" t="n">
-        <v>12.557311351392</v>
+        <v>12.54830848625804</v>
       </c>
       <c r="L240" t="n">
         <v>36.97617642820231</v>
       </c>
       <c r="M240" t="n">
-        <v>12.49945175787417</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N240" t="n">
-        <v>11.33187334346197</v>
+        <v>8.100198964353241</v>
       </c>
       <c r="O240" t="n">
-        <v>11.91566255066807</v>
+        <v>10.48534896870295</v>
       </c>
       <c r="P240" t="b">
         <v>1</v>
       </c>
       <c r="Q240" t="n">
-        <v>-5.3849192018949</v>
+        <v>-19.6746863047923</v>
       </c>
     </row>
     <row r="241">
@@ -14480,25 +14336,25 @@
         <v>6</v>
       </c>
       <c r="K241" t="n">
-        <v>12.557311351392</v>
+        <v>12.54701813750437</v>
       </c>
       <c r="L241" t="n">
         <v>37.01027578408338</v>
       </c>
       <c r="M241" t="n">
-        <v>12.49945175787417</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N241" t="n">
-        <v>11.33187334346197</v>
+        <v>10.01607876214662</v>
       </c>
       <c r="O241" t="n">
-        <v>11.91566255066807</v>
+        <v>11.44328886759964</v>
       </c>
       <c r="P241" t="b">
         <v>1</v>
       </c>
       <c r="Q241" t="n">
-        <v>-5.3849192018949</v>
+        <v>-9.645210242221602</v>
       </c>
     </row>
     <row r="242">
@@ -14539,25 +14395,25 @@
         <v>6</v>
       </c>
       <c r="K242" t="n">
-        <v>12.45332192399493</v>
+        <v>12.44763178568168</v>
       </c>
       <c r="L242" t="n">
         <v>37.18465285513517</v>
       </c>
       <c r="M242" t="n">
-        <v>12.28779173644725</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N242" t="n">
-        <v>11.1448551788642</v>
+        <v>10.01607876214662</v>
       </c>
       <c r="O242" t="n">
-        <v>11.71632345765573</v>
+        <v>11.44328886759964</v>
       </c>
       <c r="P242" t="b">
         <v>1</v>
       </c>
       <c r="Q242" t="n">
-        <v>-6.29035609167683</v>
+        <v>-8.776698112775261</v>
       </c>
     </row>
     <row r="243">
@@ -14598,25 +14454,25 @@
         <v>6</v>
       </c>
       <c r="K243" t="n">
-        <v>12.45332192399493</v>
+        <v>12.44763178568168</v>
       </c>
       <c r="L243" t="n">
         <v>37.20877667370117</v>
       </c>
       <c r="M243" t="n">
-        <v>12.28779173644725</v>
+        <v>12.87049897305267</v>
       </c>
       <c r="N243" t="n">
-        <v>11.1448551788642</v>
+        <v>10.01607876214662</v>
       </c>
       <c r="O243" t="n">
-        <v>11.71632345765573</v>
+        <v>11.44328886759964</v>
       </c>
       <c r="P243" t="b">
         <v>1</v>
       </c>
       <c r="Q243" t="n">
-        <v>-6.29035609167683</v>
+        <v>-8.776698112775261</v>
       </c>
     </row>
     <row r="244">
@@ -14657,25 +14513,25 @@
         <v>6</v>
       </c>
       <c r="K244" t="n">
-        <v>12.40593897788581</v>
+        <v>12.40318891736148</v>
       </c>
       <c r="L244" t="n">
         <v>37.32265008551443</v>
       </c>
       <c r="M244" t="n">
-        <v>12.28779173644725</v>
+        <v>12.7867235364597</v>
       </c>
       <c r="N244" t="n">
-        <v>10.98126156842115</v>
+        <v>14.33354695366698</v>
       </c>
       <c r="O244" t="n">
-        <v>11.6345266524342</v>
+        <v>13.56013524506334</v>
       </c>
       <c r="P244" t="b">
         <v>1</v>
       </c>
       <c r="Q244" t="n">
-        <v>-6.630371380774736</v>
+        <v>8.531967467824863</v>
       </c>
     </row>
     <row r="245">
@@ -14716,25 +14572,25 @@
         <v>6</v>
       </c>
       <c r="K245" t="n">
-        <v>12.19413671075773</v>
+        <v>12.18857742981998</v>
       </c>
       <c r="L245" t="n">
         <v>37.61694404515659</v>
       </c>
       <c r="M245" t="n">
-        <v>11.88832606873517</v>
+        <v>12.89096747702697</v>
       </c>
       <c r="N245" t="n">
-        <v>10.99451771464207</v>
+        <v>14.33354695366698</v>
       </c>
       <c r="O245" t="n">
-        <v>11.44142189168862</v>
+        <v>13.61225721534698</v>
       </c>
       <c r="P245" t="b">
         <v>1</v>
       </c>
       <c r="Q245" t="n">
-        <v>-6.578857297587315</v>
+        <v>10.4588075511965</v>
       </c>
     </row>
     <row r="246">
@@ -14775,25 +14631,25 @@
         <v>6</v>
       </c>
       <c r="K246" t="n">
-        <v>12.08990666231681</v>
+        <v>12.08974146158847</v>
       </c>
       <c r="L246" t="n">
         <v>37.97018193389955</v>
       </c>
       <c r="M246" t="n">
-        <v>12.16318878177189</v>
+        <v>13.05682586052934</v>
       </c>
       <c r="N246" t="n">
-        <v>11.01398975244947</v>
+        <v>2.228950017658618</v>
       </c>
       <c r="O246" t="n">
-        <v>11.58858926711068</v>
+        <v>7.642887939093981</v>
       </c>
       <c r="P246" t="b">
         <v>1</v>
       </c>
       <c r="Q246" t="n">
-        <v>-4.325957056989727</v>
+        <v>-58.18289575787811</v>
       </c>
     </row>
     <row r="247">
@@ -14834,25 +14690,25 @@
         <v>6</v>
       </c>
       <c r="K247" t="n">
-        <v>12.0907797271752</v>
+        <v>12.0911207414604</v>
       </c>
       <c r="L247" t="n">
         <v>38.0115845379872</v>
       </c>
       <c r="M247" t="n">
-        <v>12.16318878177189</v>
+        <v>13.28858676062679</v>
       </c>
       <c r="N247" t="n">
-        <v>10.94464035966949</v>
+        <v>2.228950017658618</v>
       </c>
       <c r="O247" t="n">
-        <v>11.55391457072069</v>
+        <v>7.758768389142702</v>
       </c>
       <c r="P247" t="b">
         <v>1</v>
       </c>
       <c r="Q247" t="n">
-        <v>-4.646608326281054</v>
+        <v>-55.83814511566312</v>
       </c>
     </row>
     <row r="248">
@@ -14893,25 +14749,25 @@
         <v>6</v>
       </c>
       <c r="K248" t="n">
-        <v>12.09182775173085</v>
+        <v>12.09182940507767</v>
       </c>
       <c r="L248" t="n">
         <v>38.22827150060657</v>
       </c>
       <c r="M248" t="n">
-        <v>12.16318878177189</v>
+        <v>13.28858676062679</v>
       </c>
       <c r="N248" t="n">
-        <v>10.87454393270211</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="O248" t="n">
-        <v>11.518866357237</v>
+        <v>8.103970338657385</v>
       </c>
       <c r="P248" t="b">
         <v>1</v>
       </c>
       <c r="Q248" t="n">
-        <v>-4.974112701063427</v>
+        <v>-49.20870758123932</v>
       </c>
     </row>
     <row r="249">
@@ -14952,25 +14808,25 @@
         <v>7</v>
       </c>
       <c r="K249" t="n">
-        <v>12.0953605974493</v>
+        <v>12.09598596468677</v>
       </c>
       <c r="L249" t="n">
         <v>38.36904932107526</v>
       </c>
       <c r="M249" t="n">
-        <v>12.2850933308724</v>
+        <v>13.22856214979317</v>
       </c>
       <c r="N249" t="n">
-        <v>10.78344121762455</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="O249" t="n">
-        <v>11.53426727424847</v>
+        <v>8.073958033240578</v>
       </c>
       <c r="P249" t="b">
         <v>1</v>
       </c>
       <c r="Q249" t="n">
-        <v>-4.864577088945454</v>
+        <v>-49.81482334794727</v>
       </c>
     </row>
     <row r="250">
@@ -15011,25 +14867,25 @@
         <v>7</v>
       </c>
       <c r="K250" t="n">
-        <v>12.1052150235773</v>
+        <v>12.10642473098731</v>
       </c>
       <c r="L250" t="n">
         <v>38.41570461320196</v>
       </c>
       <c r="M250" t="n">
-        <v>12.2850933308724</v>
+        <v>13.22815891986998</v>
       </c>
       <c r="N250" t="n">
-        <v>10.78344121762455</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="O250" t="n">
-        <v>11.53426727424847</v>
+        <v>8.073756418278981</v>
       </c>
       <c r="P250" t="b">
         <v>1</v>
       </c>
       <c r="Q250" t="n">
-        <v>-4.95001317165189</v>
+        <v>-49.94785702945372</v>
       </c>
     </row>
     <row r="251">
@@ -15070,25 +14926,25 @@
         <v>7</v>
       </c>
       <c r="K251" t="n">
-        <v>12.1067013623614</v>
+        <v>12.1067270130998</v>
       </c>
       <c r="L251" t="n">
         <v>38.4306127331897</v>
       </c>
       <c r="M251" t="n">
-        <v>12.2850933308724</v>
+        <v>13.22815891986998</v>
       </c>
       <c r="N251" t="n">
-        <v>10.78344121762455</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="O251" t="n">
-        <v>11.53426727424847</v>
+        <v>8.073756418278981</v>
       </c>
       <c r="P251" t="b">
         <v>1</v>
       </c>
       <c r="Q251" t="n">
-        <v>-4.962899458650027</v>
+        <v>-49.95160103777935</v>
       </c>
     </row>
     <row r="252">
@@ -15129,25 +14985,25 @@
         <v>7</v>
       </c>
       <c r="K252" t="n">
-        <v>12.1605822292569</v>
+        <v>12.16272564065115</v>
       </c>
       <c r="L252" t="n">
         <v>38.64875426228402</v>
       </c>
       <c r="M252" t="n">
-        <v>12.30729200089643</v>
+        <v>12.55278671512658</v>
       </c>
       <c r="N252" t="n">
-        <v>10.47894384845322</v>
+        <v>2.650094119750283</v>
       </c>
       <c r="O252" t="n">
-        <v>11.39311792467483</v>
+        <v>7.601440417438431</v>
       </c>
       <c r="P252" t="b">
         <v>1</v>
       </c>
       <c r="Q252" t="n">
-        <v>-6.736209610539734</v>
+        <v>-60.00553806550526</v>
       </c>
     </row>
     <row r="253">
@@ -15188,25 +15044,25 @@
         <v>7</v>
       </c>
       <c r="K253" t="n">
-        <v>12.229154793299</v>
+        <v>12.2311785122366</v>
       </c>
       <c r="L253" t="n">
         <v>38.76428355645489</v>
       </c>
       <c r="M253" t="n">
-        <v>12.46602379984828</v>
+        <v>12.55278671512658</v>
       </c>
       <c r="N253" t="n">
-        <v>10.40804462411561</v>
+        <v>2.281063470489664</v>
       </c>
       <c r="O253" t="n">
-        <v>11.43703421198194</v>
+        <v>7.416925092808121</v>
       </c>
       <c r="P253" t="b">
         <v>1</v>
       </c>
       <c r="Q253" t="n">
-        <v>-6.925926482647049</v>
+        <v>-64.90902037148332</v>
       </c>
     </row>
     <row r="254">
@@ -15247,25 +15103,25 @@
         <v>7</v>
       </c>
       <c r="K254" t="n">
-        <v>12.39318867506093</v>
+        <v>12.39841015681416</v>
       </c>
       <c r="L254" t="n">
         <v>38.98539876576569</v>
       </c>
       <c r="M254" t="n">
-        <v>12.49982119715622</v>
+        <v>12.29751099175077</v>
       </c>
       <c r="N254" t="n">
-        <v>10.38102462126298</v>
+        <v>0.9024303134160061</v>
       </c>
       <c r="O254" t="n">
-        <v>11.4404229092096</v>
+        <v>6.59997065258339</v>
       </c>
       <c r="P254" t="b">
         <v>1</v>
       </c>
       <c r="Q254" t="n">
-        <v>-8.328064210671293</v>
+        <v>-87.85553466000815</v>
       </c>
     </row>
     <row r="255">
@@ -15306,26 +15162,20 @@
         <v>7</v>
       </c>
       <c r="K255" t="n">
-        <v>12.63399979306722</v>
+        <v>12.63438262869062</v>
       </c>
       <c r="L255" t="n">
         <v>39.1933439419829</v>
       </c>
       <c r="M255" t="n">
-        <v>12.52439545881572</v>
-      </c>
-      <c r="N255" t="n">
-        <v>9.865992057560909</v>
-      </c>
-      <c r="O255" t="n">
-        <v>11.19519375818831</v>
-      </c>
+        <v>12.29277387507475</v>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
       <c r="P255" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>-12.85199761573173</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -15365,26 +15215,20 @@
         <v>7</v>
       </c>
       <c r="K256" t="n">
-        <v>12.77277566475786</v>
+        <v>12.6423103050087</v>
       </c>
       <c r="L256" t="n">
         <v>39.27729121113223</v>
       </c>
       <c r="M256" t="n">
-        <v>12.52439545881572</v>
-      </c>
-      <c r="N256" t="n">
-        <v>9.865992057560909</v>
-      </c>
-      <c r="O256" t="n">
-        <v>11.19519375818831</v>
-      </c>
+        <v>12.29958707864683</v>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
       <c r="P256" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q256" t="n">
-        <v>-14.09159984761923</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -15424,26 +15268,20 @@
         <v>7</v>
       </c>
       <c r="K257" t="n">
-        <v>12.92361940445302</v>
+        <v>12.93319383577244</v>
       </c>
       <c r="L257" t="n">
         <v>39.42374720779748</v>
       </c>
       <c r="M257" t="n">
-        <v>12.54340224967523</v>
-      </c>
-      <c r="N257" t="n">
-        <v>9.865992057560909</v>
-      </c>
-      <c r="O257" t="n">
-        <v>11.20469715361807</v>
-      </c>
+        <v>12.3111585689887</v>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
       <c r="P257" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q257" t="n">
-        <v>-15.34108621829107</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -15483,26 +15321,20 @@
         <v>7</v>
       </c>
       <c r="K258" t="n">
-        <v>13.00581980539971</v>
+        <v>12.99985311520591</v>
       </c>
       <c r="L258" t="n">
         <v>39.80525062801659</v>
       </c>
       <c r="M258" t="n">
-        <v>12.55626785778556</v>
-      </c>
-      <c r="N258" t="n">
-        <v>9.555805411166167</v>
-      </c>
-      <c r="O258" t="n">
-        <v>11.05603663447586</v>
-      </c>
+        <v>12.35342338176835</v>
+      </c>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
       <c r="P258" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>-17.63546228531727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -15542,26 +15374,20 @@
         <v>7</v>
       </c>
       <c r="K259" t="n">
-        <v>11.21371983920643</v>
+        <v>11.20503957697606</v>
       </c>
       <c r="L259" t="n">
         <v>40.00975222420364</v>
       </c>
       <c r="M259" t="n">
-        <v>12.55626785778556</v>
-      </c>
-      <c r="N259" t="n">
-        <v>9.780307074547082</v>
-      </c>
-      <c r="O259" t="n">
-        <v>11.16828746616632</v>
-      </c>
+        <v>12.50552073045885</v>
+      </c>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
       <c r="P259" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q259" t="n">
-        <v>-0.4067980268035454</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -15601,26 +15427,20 @@
         <v>7</v>
       </c>
       <c r="K260" t="n">
-        <v>10.91295735455809</v>
+        <v>10.90825101063755</v>
       </c>
       <c r="L260" t="n">
         <v>40.3108801591185</v>
       </c>
       <c r="M260" t="n">
-        <v>12.71883627017913</v>
-      </c>
-      <c r="N260" t="n">
-        <v>10.12109543564426</v>
-      </c>
-      <c r="O260" t="n">
-        <v>11.41996585291169</v>
-      </c>
+        <v>12.64447152506395</v>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
       <c r="P260" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q260" t="n">
-        <v>4.439667376276213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -15660,26 +15480,20 @@
         <v>7</v>
       </c>
       <c r="K261" t="n">
-        <v>10.90630933043323</v>
+        <v>10.90493944776398</v>
       </c>
       <c r="L261" t="n">
         <v>40.35255223610768</v>
       </c>
       <c r="M261" t="n">
-        <v>12.71883627017913</v>
-      </c>
-      <c r="N261" t="n">
-        <v>10.12109543564426</v>
-      </c>
-      <c r="O261" t="n">
-        <v>11.41996585291169</v>
-      </c>
+        <v>12.64447152506395</v>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
       <c r="P261" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q261" t="n">
-        <v>4.497881421838946</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -15719,26 +15533,20 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>11.11067537123716</v>
+        <v>11.11747203295466</v>
       </c>
       <c r="L262" t="n">
         <v>40.81938972703808</v>
       </c>
       <c r="M262" t="n">
-        <v>12.54480457182633</v>
-      </c>
-      <c r="N262" t="n">
-        <v>24.49874699689521</v>
-      </c>
-      <c r="O262" t="n">
-        <v>18.52177578436077</v>
-      </c>
+        <v>12.82934323440308</v>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
       <c r="P262" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q262" t="n">
-        <v>40.01290426688635</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -15778,26 +15586,20 @@
         <v>7</v>
       </c>
       <c r="K263" t="n">
-        <v>11.12092613981406</v>
+        <v>11.12288100999922</v>
       </c>
       <c r="L263" t="n">
         <v>40.8393068952863</v>
       </c>
       <c r="M263" t="n">
-        <v>12.5861789188918</v>
-      </c>
-      <c r="N263" t="n">
-        <v>24.49874699689521</v>
-      </c>
-      <c r="O263" t="n">
-        <v>18.54246295789351</v>
-      </c>
+        <v>12.82934323440308</v>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
       <c r="P263" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>40.0245470891994</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -15837,26 +15639,20 @@
         <v>7</v>
       </c>
       <c r="K264" t="n">
-        <v>11.41452067011062</v>
+        <v>11.32387376443929</v>
       </c>
       <c r="L264" t="n">
         <v>41.08654447624548</v>
       </c>
       <c r="M264" t="n">
-        <v>12.54329025449246</v>
-      </c>
-      <c r="N264" t="n">
-        <v>27.2219322171788</v>
-      </c>
-      <c r="O264" t="n">
-        <v>19.88261123583563</v>
-      </c>
+        <v>12.90839304015632</v>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
       <c r="P264" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q264" t="n">
-        <v>42.59043475367288</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -15896,26 +15692,20 @@
         <v>7</v>
       </c>
       <c r="K265" t="n">
-        <v>11.41803390508936</v>
+        <v>11.42106618993412</v>
       </c>
       <c r="L265" t="n">
         <v>41.13303638646497</v>
       </c>
       <c r="M265" t="n">
-        <v>12.54329025449246</v>
-      </c>
-      <c r="N265" t="n">
-        <v>27.2219322171788</v>
-      </c>
-      <c r="O265" t="n">
-        <v>19.88261123583563</v>
-      </c>
+        <v>12.90839304015632</v>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
       <c r="P265" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q265" t="n">
-        <v>42.57276486646811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -15955,26 +15745,20 @@
         <v>7</v>
       </c>
       <c r="K266" t="n">
-        <v>11.42474323728245</v>
+        <v>11.42637066840364</v>
       </c>
       <c r="L266" t="n">
         <v>41.14936571487551</v>
       </c>
       <c r="M266" t="n">
-        <v>12.47729707886387</v>
-      </c>
-      <c r="N266" t="n">
-        <v>27.2219322171788</v>
-      </c>
-      <c r="O266" t="n">
-        <v>19.84961464802133</v>
-      </c>
+        <v>12.90839304015632</v>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
       <c r="P266" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q266" t="n">
-        <v>42.4435010962729</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -16014,26 +15798,20 @@
         <v>7</v>
       </c>
       <c r="K267" t="n">
-        <v>11.52098055181535</v>
+        <v>11.52264720329341</v>
       </c>
       <c r="L267" t="n">
         <v>41.24839825029503</v>
       </c>
       <c r="M267" t="n">
-        <v>12.47729707886387</v>
-      </c>
-      <c r="N267" t="n">
-        <v>13.33689779326027</v>
-      </c>
-      <c r="O267" t="n">
-        <v>12.90709743606207</v>
-      </c>
+        <v>12.90839304015632</v>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
       <c r="P267" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q267" t="n">
-        <v>10.73918354698362</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -16073,26 +15851,20 @@
         <v>7</v>
       </c>
       <c r="K268" t="n">
-        <v>11.60063562855445</v>
+        <v>11.60571276836865</v>
       </c>
       <c r="L268" t="n">
         <v>41.32873972660931</v>
       </c>
       <c r="M268" t="n">
-        <v>12.47721645407332</v>
-      </c>
-      <c r="N268" t="n">
-        <v>13.33689779326027</v>
-      </c>
-      <c r="O268" t="n">
-        <v>12.90705712366679</v>
-      </c>
+        <v>12.80505334864713</v>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
       <c r="P268" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q268" t="n">
-        <v>10.12176116209205</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -16132,26 +15904,20 @@
         <v>7</v>
       </c>
       <c r="K269" t="n">
-        <v>11.63492252765004</v>
+        <v>11.63462537719781</v>
       </c>
       <c r="L269" t="n">
         <v>41.44986287543508</v>
       </c>
       <c r="M269" t="n">
-        <v>12.49451825327216</v>
-      </c>
-      <c r="N269" t="n">
-        <v>13.33689779326027</v>
-      </c>
-      <c r="O269" t="n">
-        <v>12.91570802326622</v>
-      </c>
+        <v>12.80470013952624</v>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
       <c r="P269" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q269" t="n">
-        <v>9.916494653711483</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -16191,26 +15957,20 @@
         <v>7</v>
       </c>
       <c r="K270" t="n">
-        <v>11.59571903340261</v>
+        <v>11.59495023728868</v>
       </c>
       <c r="L270" t="n">
         <v>41.54546897966951</v>
       </c>
       <c r="M270" t="n">
-        <v>12.49451825327216</v>
-      </c>
-      <c r="N270" t="n">
-        <v>8.889316939855588</v>
-      </c>
-      <c r="O270" t="n">
-        <v>10.69191759656388</v>
-      </c>
+        <v>12.73965880607229</v>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
       <c r="P270" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>-8.453127595457644</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -16250,26 +16010,20 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>11.47482411747132</v>
+        <v>11.47413396052639</v>
       </c>
       <c r="L271" t="n">
         <v>41.75244033759741</v>
       </c>
       <c r="M271" t="n">
-        <v>12.5438949370723</v>
-      </c>
-      <c r="N271" t="n">
-        <v>7.895758218956223</v>
-      </c>
-      <c r="O271" t="n">
-        <v>10.21982657801426</v>
-      </c>
+        <v>12.66848637001136</v>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
       <c r="P271" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q271" t="n">
-        <v>-12.28002774682018</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -16309,26 +16063,20 @@
         <v>7</v>
       </c>
       <c r="K272" t="n">
-        <v>11.41973742778242</v>
+        <v>11.41489990968029</v>
       </c>
       <c r="L272" t="n">
         <v>41.81468525727337</v>
       </c>
       <c r="M272" t="n">
-        <v>12.5438949370723</v>
-      </c>
-      <c r="N272" t="n">
-        <v>7.895758218956223</v>
-      </c>
-      <c r="O272" t="n">
-        <v>10.21982657801426</v>
-      </c>
+        <v>12.50157920325796</v>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
       <c r="P272" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q272" t="n">
-        <v>-11.74100989491846</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -16368,26 +16116,20 @@
         <v>7</v>
       </c>
       <c r="K273" t="n">
-        <v>11.41973742778242</v>
+        <v>11.41489990968029</v>
       </c>
       <c r="L273" t="n">
         <v>41.82882141361956</v>
       </c>
       <c r="M273" t="n">
-        <v>12.5438949370723</v>
-      </c>
-      <c r="N273" t="n">
-        <v>7.895758218956223</v>
-      </c>
-      <c r="O273" t="n">
-        <v>10.21982657801426</v>
-      </c>
+        <v>12.50157920325796</v>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
       <c r="P273" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q273" t="n">
-        <v>-11.74100989491846</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -16427,26 +16169,20 @@
         <v>7</v>
       </c>
       <c r="K274" t="n">
-        <v>11.33187334346197</v>
+        <v>11.32954314383762</v>
       </c>
       <c r="L274" t="n">
         <v>41.93701778991529</v>
       </c>
       <c r="M274" t="n">
-        <v>12.55371901573918</v>
-      </c>
-      <c r="N274" t="n">
-        <v>8.095440007033142</v>
-      </c>
-      <c r="O274" t="n">
-        <v>10.32457951138616</v>
-      </c>
+        <v>12.50157920325796</v>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
       <c r="P274" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q274" t="n">
-        <v>-9.756269792536809</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -16486,26 +16222,20 @@
         <v>7</v>
       </c>
       <c r="K275" t="n">
-        <v>11.1448551788642</v>
+        <v>11.13895581474152</v>
       </c>
       <c r="L275" t="n">
         <v>42.0989421781486</v>
       </c>
       <c r="M275" t="n">
-        <v>12.45332192399493</v>
-      </c>
-      <c r="N275" t="n">
-        <v>10.00684862315599</v>
-      </c>
-      <c r="O275" t="n">
-        <v>11.23008527357546</v>
-      </c>
+        <v>12.27482045438042</v>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
       <c r="P275" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q275" t="n">
-        <v>0.7589443235289428</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -16545,26 +16275,20 @@
         <v>7</v>
       </c>
       <c r="K276" t="n">
-        <v>10.98126156842115</v>
+        <v>10.97826395037231</v>
       </c>
       <c r="L276" t="n">
         <v>42.33240217987535</v>
       </c>
       <c r="M276" t="n">
-        <v>12.40593897788581</v>
-      </c>
-      <c r="N276" t="n">
-        <v>14.32297963039842</v>
-      </c>
-      <c r="O276" t="n">
-        <v>13.36445930414211</v>
-      </c>
+        <v>12.27482045438042</v>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
       <c r="P276" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>17.83235431741203</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -16604,26 +16328,20 @@
         <v>7</v>
       </c>
       <c r="K277" t="n">
-        <v>10.93366607274151</v>
+        <v>10.93181450941635</v>
       </c>
       <c r="L277" t="n">
         <v>42.40455060806124</v>
       </c>
       <c r="M277" t="n">
-        <v>12.40593897788581</v>
-      </c>
-      <c r="N277" t="n">
-        <v>14.32297963039842</v>
-      </c>
-      <c r="O277" t="n">
-        <v>13.36445930414211</v>
-      </c>
+        <v>12.27482045438042</v>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
       <c r="P277" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>18.1884891568132</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -16663,26 +16381,20 @@
         <v>7</v>
       </c>
       <c r="K278" t="n">
-        <v>10.99451771464207</v>
+        <v>10.99471119916965</v>
       </c>
       <c r="L278" t="n">
         <v>42.77859709364042</v>
       </c>
       <c r="M278" t="n">
-        <v>12.19413671075773</v>
-      </c>
-      <c r="N278" t="n">
-        <v>2.216074922761316</v>
-      </c>
-      <c r="O278" t="n">
-        <v>7.205105816759523</v>
-      </c>
+        <v>11.88670746705587</v>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
       <c r="P278" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>-52.59342463879078</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -16722,26 +16434,20 @@
         <v>7</v>
       </c>
       <c r="K279" t="n">
-        <v>11.01398975244947</v>
+        <v>11.01403501917856</v>
       </c>
       <c r="L279" t="n">
         <v>42.85448096625999</v>
       </c>
       <c r="M279" t="n">
-        <v>12.08990666231681</v>
-      </c>
-      <c r="N279" t="n">
-        <v>2.216074922761316</v>
-      </c>
-      <c r="O279" t="n">
-        <v>7.152990792539062</v>
-      </c>
+        <v>11.88670746705587</v>
+      </c>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>-53.97740709994525</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -16781,26 +16487,20 @@
         <v>7</v>
       </c>
       <c r="K280" t="n">
-        <v>10.94464035966949</v>
+        <v>10.98360851806071</v>
       </c>
       <c r="L280" t="n">
         <v>43.09255095470977</v>
       </c>
       <c r="M280" t="n">
-        <v>12.0907797271752</v>
-      </c>
-      <c r="N280" t="n">
-        <v>2.228411948180104</v>
-      </c>
-      <c r="O280" t="n">
-        <v>7.15959583767765</v>
-      </c>
+        <v>12.16944965305047</v>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
       <c r="P280" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q280" t="n">
-        <v>-52.86673448901815</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -16840,26 +16540,20 @@
         <v>7</v>
       </c>
       <c r="K281" t="n">
-        <v>10.87454393270211</v>
+        <v>10.87185681435206</v>
       </c>
       <c r="L281" t="n">
         <v>43.24353956846407</v>
       </c>
       <c r="M281" t="n">
-        <v>12.09182775173085</v>
-      </c>
-      <c r="N281" t="n">
-        <v>2.918636786978264</v>
-      </c>
-      <c r="O281" t="n">
-        <v>7.505232269354556</v>
-      </c>
+        <v>12.16944965305047</v>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
       <c r="P281" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q281" t="n">
-        <v>-44.89283665617072</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -16899,26 +16593,20 @@
         <v>7</v>
       </c>
       <c r="K282" t="n">
-        <v>10.8697265650179</v>
+        <v>10.86892360754432</v>
       </c>
       <c r="L282" t="n">
         <v>43.25157522983871</v>
       </c>
       <c r="M282" t="n">
-        <v>12.09182775173085</v>
-      </c>
-      <c r="N282" t="n">
-        <v>2.918636786978264</v>
-      </c>
-      <c r="O282" t="n">
-        <v>7.505232269354556</v>
-      </c>
+        <v>12.16944965305047</v>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
       <c r="P282" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>-44.82864986605788</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -16958,26 +16646,20 @@
         <v>7</v>
       </c>
       <c r="K283" t="n">
-        <v>10.78344121762455</v>
+        <v>10.77889366400938</v>
       </c>
       <c r="L283" t="n">
         <v>43.30177734443766</v>
       </c>
       <c r="M283" t="n">
-        <v>12.0953605974493</v>
-      </c>
-      <c r="N283" t="n">
-        <v>2.918636786978264</v>
-      </c>
-      <c r="O283" t="n">
-        <v>7.506998692213781</v>
-      </c>
+        <v>12.16944965305047</v>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
       <c r="P283" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q283" t="n">
-        <v>-43.64517245499291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -17017,26 +16699,20 @@
         <v>7</v>
       </c>
       <c r="K284" t="n">
-        <v>10.47894384845322</v>
+        <v>10.52198977187999</v>
       </c>
       <c r="L284" t="n">
         <v>43.66342875604664</v>
       </c>
       <c r="M284" t="n">
-        <v>12.1605822292569</v>
-      </c>
-      <c r="N284" t="n">
-        <v>2.651124100366764</v>
-      </c>
-      <c r="O284" t="n">
-        <v>7.40585316481183</v>
-      </c>
+        <v>12.46436863874414</v>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
       <c r="P284" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q284" t="n">
-        <v>-41.49543091460244</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -17076,26 +16752,20 @@
         <v>7</v>
       </c>
       <c r="K285" t="n">
-        <v>10.40804462411561</v>
+        <v>10.41206116985837</v>
       </c>
       <c r="L285" t="n">
         <v>43.70186155743665</v>
       </c>
       <c r="M285" t="n">
-        <v>12.1605822292569</v>
-      </c>
-      <c r="N285" t="n">
-        <v>2.282047730268187</v>
-      </c>
-      <c r="O285" t="n">
-        <v>7.221314979762542</v>
-      </c>
+        <v>12.46436863874414</v>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
       <c r="P285" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>-44.12949238862667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -17135,26 +16805,20 @@
         <v>7</v>
       </c>
       <c r="K286" t="n">
-        <v>10.40804462411561</v>
+        <v>10.41206116985837</v>
       </c>
       <c r="L286" t="n">
         <v>43.73248112749065</v>
       </c>
       <c r="M286" t="n">
-        <v>12.229154793299</v>
-      </c>
-      <c r="N286" t="n">
-        <v>2.282047730268187</v>
-      </c>
-      <c r="O286" t="n">
-        <v>7.255601261783596</v>
-      </c>
+        <v>12.46436863874414</v>
+      </c>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
       <c r="P286" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q286" t="n">
-        <v>-43.44840969881343</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -17194,26 +16858,20 @@
         <v>7</v>
       </c>
       <c r="K287" t="n">
-        <v>10.38102462126298</v>
+        <v>10.37866941025346</v>
       </c>
       <c r="L287" t="n">
         <v>43.91481188926387</v>
       </c>
       <c r="M287" t="n">
-        <v>12.39318867506093</v>
-      </c>
-      <c r="N287" t="n">
-        <v>0.9026450154184265</v>
-      </c>
-      <c r="O287" t="n">
-        <v>6.647916845239677</v>
-      </c>
+        <v>12.49027804851815</v>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
       <c r="P287" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>-56.15454980753021</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -17253,13 +16911,13 @@
         <v>7</v>
       </c>
       <c r="K288" t="n">
-        <v>9.865992057560909</v>
+        <v>9.863821606315435</v>
       </c>
       <c r="L288" t="n">
         <v>44.31951468702746</v>
       </c>
       <c r="M288" t="n">
-        <v>12.77277566475786</v>
+        <v>12.54276937654406</v>
       </c>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
@@ -17306,13 +16964,13 @@
         <v>7</v>
       </c>
       <c r="K289" t="n">
-        <v>9.865992057560909</v>
+        <v>9.863821606315435</v>
       </c>
       <c r="L289" t="n">
         <v>44.3698033738984</v>
       </c>
       <c r="M289" t="n">
-        <v>12.92361940445302</v>
+        <v>12.54276937654406</v>
       </c>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
@@ -17359,13 +17017,13 @@
         <v>7</v>
       </c>
       <c r="K290" t="n">
-        <v>9.707258352346917</v>
+        <v>9.705319379086149</v>
       </c>
       <c r="L290" t="n">
         <v>44.50420156316382</v>
       </c>
       <c r="M290" t="n">
-        <v>12.92361940445302</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
@@ -17412,13 +17070,13 @@
         <v>7</v>
       </c>
       <c r="K291" t="n">
-        <v>9.707258352346917</v>
+        <v>9.705319379086149</v>
       </c>
       <c r="L291" t="n">
         <v>44.51218096158321</v>
       </c>
       <c r="M291" t="n">
-        <v>12.92361940445302</v>
+        <v>12.57750305453999</v>
       </c>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr"/>
@@ -17465,13 +17123,13 @@
         <v>7</v>
       </c>
       <c r="K292" t="n">
-        <v>9.585453790496352</v>
+        <v>9.584177558771005</v>
       </c>
       <c r="L292" t="n">
         <v>44.70802949029083</v>
       </c>
       <c r="M292" t="n">
-        <v>13.00581980539971</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr"/>
@@ -17518,13 +17176,13 @@
         <v>7</v>
       </c>
       <c r="K293" t="n">
-        <v>9.555805411166167</v>
+        <v>9.555403531742021</v>
       </c>
       <c r="L293" t="n">
         <v>44.87052483869067</v>
       </c>
       <c r="M293" t="n">
-        <v>13.00581980539971</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
@@ -17571,13 +17229,13 @@
         <v>7</v>
       </c>
       <c r="K294" t="n">
-        <v>9.589824374387744</v>
+        <v>9.555403531742021</v>
       </c>
       <c r="L294" t="n">
         <v>44.90420085133194</v>
       </c>
       <c r="M294" t="n">
-        <v>13.00581980539971</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
@@ -17624,13 +17282,13 @@
         <v>7</v>
       </c>
       <c r="K295" t="n">
-        <v>9.780307074547082</v>
+        <v>9.785260887277799</v>
       </c>
       <c r="L295" t="n">
         <v>45.03085501260981</v>
       </c>
       <c r="M295" t="n">
-        <v>11.21371983920643</v>
+        <v>12.55976736519636</v>
       </c>
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr"/>
@@ -17677,13 +17335,13 @@
         <v>7</v>
       </c>
       <c r="K296" t="n">
-        <v>9.998318869628216</v>
+        <v>10.00254196239758</v>
       </c>
       <c r="L296" t="n">
         <v>45.12779932575243</v>
       </c>
       <c r="M296" t="n">
-        <v>11.21371983920643</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
@@ -17730,13 +17388,13 @@
         <v>7</v>
       </c>
       <c r="K297" t="n">
-        <v>9.998318869628216</v>
+        <v>10.00254196239758</v>
       </c>
       <c r="L297" t="n">
         <v>45.17649045936579</v>
       </c>
       <c r="M297" t="n">
-        <v>10.91295735455809</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr"/>
@@ -17783,13 +17441,13 @@
         <v>7</v>
       </c>
       <c r="K298" t="n">
-        <v>10.12109543564426</v>
+        <v>10.12230649472664</v>
       </c>
       <c r="L298" t="n">
         <v>45.24833958473766</v>
       </c>
       <c r="M298" t="n">
-        <v>10.91295735455809</v>
+        <v>12.71757990463073</v>
       </c>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
@@ -17836,13 +17494,13 @@
         <v>7</v>
       </c>
       <c r="K299" t="n">
-        <v>10.46365288464387</v>
+        <v>10.47758980818898</v>
       </c>
       <c r="L299" t="n">
         <v>45.58067892950262</v>
       </c>
       <c r="M299" t="n">
-        <v>10.90630933043323</v>
+        <v>12.60397629558391</v>
       </c>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
@@ -17889,13 +17547,13 @@
         <v>7</v>
       </c>
       <c r="K300" t="n">
-        <v>20.00662029277056</v>
+        <v>20.11034191780546</v>
       </c>
       <c r="L300" t="n">
         <v>45.67101734885589</v>
       </c>
       <c r="M300" t="n">
-        <v>11.11067537123716</v>
+        <v>12.56827758091871</v>
       </c>
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr"/>
@@ -17942,13 +17600,13 @@
         <v>7</v>
       </c>
       <c r="K301" t="n">
-        <v>24.49874699689521</v>
+        <v>24.57628309984061</v>
       </c>
       <c r="L301" t="n">
         <v>45.78398946198521</v>
       </c>
       <c r="M301" t="n">
-        <v>11.11067537123716</v>
+        <v>12.5514918954519</v>
       </c>
       <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr"/>
@@ -17995,13 +17653,13 @@
         <v>7</v>
       </c>
       <c r="K302" t="n">
-        <v>27.2219322171788</v>
+        <v>27.18225840910968</v>
       </c>
       <c r="L302" t="n">
         <v>46.10673058679853</v>
       </c>
       <c r="M302" t="n">
-        <v>11.41452067011062</v>
+        <v>12.57450141296879</v>
       </c>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr"/>
@@ -18048,13 +17706,13 @@
         <v>8</v>
       </c>
       <c r="K303" t="n">
-        <v>13.33689779326027</v>
+        <v>13.29960713304792</v>
       </c>
       <c r="L303" t="n">
         <v>46.32868003531105</v>
       </c>
       <c r="M303" t="n">
-        <v>11.60063562855445</v>
+        <v>12.48340261345813</v>
       </c>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
@@ -18101,13 +17759,13 @@
         <v>8</v>
       </c>
       <c r="K304" t="n">
-        <v>13.33689779326027</v>
+        <v>13.29960713304792</v>
       </c>
       <c r="L304" t="n">
         <v>46.34404896155906</v>
       </c>
       <c r="M304" t="n">
-        <v>11.60063562855445</v>
+        <v>12.48340261345813</v>
       </c>
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
@@ -18154,13 +17812,13 @@
         <v>8</v>
       </c>
       <c r="K305" t="n">
-        <v>8.889316939855588</v>
+        <v>8.866998949237681</v>
       </c>
       <c r="L305" t="n">
         <v>46.60539880138858</v>
       </c>
       <c r="M305" t="n">
-        <v>11.59571903340261</v>
+        <v>12.48668153897131</v>
       </c>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
@@ -18207,13 +17865,13 @@
         <v>8</v>
       </c>
       <c r="K306" t="n">
-        <v>7.895758218956223</v>
+        <v>7.896421559362166</v>
       </c>
       <c r="L306" t="n">
         <v>46.8108467377976</v>
       </c>
       <c r="M306" t="n">
-        <v>11.41973742778242</v>
+        <v>12.5439341252388</v>
       </c>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
@@ -18260,13 +17918,13 @@
         <v>8</v>
       </c>
       <c r="K307" t="n">
-        <v>8.095440007033142</v>
+        <v>8.100198964353241</v>
       </c>
       <c r="L307" t="n">
         <v>46.88842933165827</v>
       </c>
       <c r="M307" t="n">
-        <v>11.33187334346197</v>
+        <v>12.54848340969551</v>
       </c>
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr"/>
@@ -18313,13 +17971,13 @@
         <v>8</v>
       </c>
       <c r="K308" t="n">
-        <v>10.00684862315599</v>
+        <v>10.01607876214662</v>
       </c>
       <c r="L308" t="n">
         <v>47.10229147257217</v>
       </c>
       <c r="M308" t="n">
-        <v>11.1448551788642</v>
+        <v>12.44763178568168</v>
       </c>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
@@ -18366,13 +18024,13 @@
         <v>8</v>
       </c>
       <c r="K309" t="n">
-        <v>14.32297963039842</v>
+        <v>14.33354695366698</v>
       </c>
       <c r="L309" t="n">
         <v>47.46442026158016</v>
       </c>
       <c r="M309" t="n">
-        <v>10.93366607274151</v>
+        <v>12.40318891736148</v>
       </c>
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
@@ -18419,13 +18077,13 @@
         <v>19</v>
       </c>
       <c r="K310" t="n">
-        <v>2.216074922761316</v>
+        <v>2.215608857004326</v>
       </c>
       <c r="L310" t="n">
         <v>47.79450144483094</v>
       </c>
       <c r="M310" t="n">
-        <v>10.99451771464207</v>
+        <v>12.08974146158847</v>
       </c>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
@@ -18472,13 +18130,13 @@
         <v>19</v>
       </c>
       <c r="K311" t="n">
-        <v>2.228411948180104</v>
+        <v>2.228950017658618</v>
       </c>
       <c r="L311" t="n">
         <v>47.92702120554764</v>
       </c>
       <c r="M311" t="n">
-        <v>11.01398975244947</v>
+        <v>12.08974146158847</v>
       </c>
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
@@ -18525,13 +18183,13 @@
         <v>19</v>
       </c>
       <c r="K312" t="n">
-        <v>2.918636786978264</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="L312" t="n">
         <v>48.28800571069628</v>
       </c>
       <c r="M312" t="n">
-        <v>10.78344121762455</v>
+        <v>12.09182940507767</v>
       </c>
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
@@ -18578,13 +18236,13 @@
         <v>19</v>
       </c>
       <c r="K313" t="n">
-        <v>2.918636786978264</v>
+        <v>2.919353916687986</v>
       </c>
       <c r="L313" t="n">
         <v>48.35924176741078</v>
       </c>
       <c r="M313" t="n">
-        <v>10.78344121762455</v>
+        <v>12.09598596468677</v>
       </c>
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr"/>
@@ -18631,13 +18289,13 @@
         <v>19</v>
       </c>
       <c r="K314" t="n">
-        <v>2.651124100366764</v>
+        <v>2.650094119750283</v>
       </c>
       <c r="L314" t="n">
         <v>48.63918016746815</v>
       </c>
       <c r="M314" t="n">
-        <v>10.47894384845322</v>
+        <v>12.16272564065115</v>
       </c>
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
@@ -18684,13 +18342,13 @@
         <v>19</v>
       </c>
       <c r="K315" t="n">
-        <v>2.282047730268187</v>
+        <v>2.281063470489664</v>
       </c>
       <c r="L315" t="n">
         <v>48.75053510427121</v>
       </c>
       <c r="M315" t="n">
-        <v>10.40804462411561</v>
+        <v>12.2311785122366</v>
       </c>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
@@ -18737,13 +18395,13 @@
         <v>19</v>
       </c>
       <c r="K316" t="n">
-        <v>0.9026450154184265</v>
+        <v>0.9024303134160061</v>
       </c>
       <c r="L316" t="n">
         <v>49.05559889721907</v>
       </c>
       <c r="M316" t="n">
-        <v>10.38102462126298</v>
+        <v>12.39841015681416</v>
       </c>
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
@@ -18790,13 +18448,13 @@
         <v>19</v>
       </c>
       <c r="K317" t="n">
-        <v>0.739985368264957</v>
+        <v>0.7400032232252212</v>
       </c>
       <c r="L317" t="n">
         <v>49.17851029220168</v>
       </c>
       <c r="M317" t="n">
-        <v>9.865992057560909</v>
+        <v>12.63438262869062</v>
       </c>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
